--- a/downloads/west-bengal.xlsx
+++ b/downloads/west-bengal.xlsx
@@ -880,13 +880,13 @@
         <v>13079</v>
       </c>
       <c r="I2" t="n">
-        <v>5.51</v>
+        <v>5.5071</v>
       </c>
       <c r="J2" t="n">
-        <v>48.73</v>
+        <v>48.7288</v>
       </c>
       <c r="K2" t="n">
-        <v>48.21</v>
+        <v>48.2071</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>218859</v>
       </c>
       <c r="P2" t="n">
-        <v>97.53</v>
+        <v>97.52509999999999</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -948,13 +948,13 @@
         <v>16173</v>
       </c>
       <c r="I3" t="n">
-        <v>6.1</v>
+        <v>6.1046</v>
       </c>
       <c r="J3" t="n">
-        <v>48.39</v>
+        <v>48.3879</v>
       </c>
       <c r="K3" t="n">
-        <v>48.01</v>
+        <v>48.0087</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>241845</v>
       </c>
       <c r="P3" t="n">
-        <v>97.22</v>
+        <v>97.2214</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -1016,13 +1016,13 @@
         <v>28224</v>
       </c>
       <c r="I4" t="n">
-        <v>9.69</v>
+        <v>9.6889</v>
       </c>
       <c r="J4" t="n">
-        <v>48.17</v>
+        <v>48.1658</v>
       </c>
       <c r="K4" t="n">
-        <v>48.21</v>
+        <v>48.2074</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>254175</v>
       </c>
       <c r="P4" t="n">
-        <v>96.62</v>
+        <v>96.61579999999999</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1084,13 +1084,13 @@
         <v>27012</v>
       </c>
       <c r="I5" t="n">
-        <v>11.21</v>
+        <v>11.2092</v>
       </c>
       <c r="J5" t="n">
-        <v>48.7</v>
+        <v>48.704</v>
       </c>
       <c r="K5" t="n">
-        <v>48.87</v>
+        <v>48.8718</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>205413</v>
       </c>
       <c r="P5" t="n">
-        <v>96</v>
+        <v>96.0017</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1152,13 +1152,13 @@
         <v>18738</v>
       </c>
       <c r="I6" t="n">
-        <v>6.16</v>
+        <v>6.158</v>
       </c>
       <c r="J6" t="n">
-        <v>47.74</v>
+        <v>47.7436</v>
       </c>
       <c r="K6" t="n">
-        <v>47.07</v>
+        <v>47.073</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>279822</v>
       </c>
       <c r="P6" t="n">
-        <v>97.98999999999999</v>
+        <v>97.99469999999999</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1220,13 +1220,13 @@
         <v>30870</v>
       </c>
       <c r="I7" t="n">
-        <v>10.15</v>
+        <v>10.1547</v>
       </c>
       <c r="J7" t="n">
-        <v>48.14</v>
+        <v>48.1381</v>
       </c>
       <c r="K7" t="n">
-        <v>47.59</v>
+        <v>47.5945</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>265319</v>
       </c>
       <c r="P7" t="n">
-        <v>97.14</v>
+        <v>97.1416</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1288,13 +1288,13 @@
         <v>29464</v>
       </c>
       <c r="I8" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6051</v>
       </c>
       <c r="J8" t="n">
-        <v>48.77</v>
+        <v>48.7725</v>
       </c>
       <c r="K8" t="n">
-        <v>48.24</v>
+        <v>48.2446</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>267925</v>
       </c>
       <c r="P8" t="n">
-        <v>96.62</v>
+        <v>96.6223</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1356,13 +1356,13 @@
         <v>14721</v>
       </c>
       <c r="I9" t="n">
-        <v>5.78</v>
+        <v>5.781</v>
       </c>
       <c r="J9" t="n">
-        <v>49.05</v>
+        <v>49.0489</v>
       </c>
       <c r="K9" t="n">
-        <v>48.63</v>
+        <v>48.6277</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>232716</v>
       </c>
       <c r="P9" t="n">
-        <v>97</v>
+        <v>96.9961</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>7583</v>
       </c>
       <c r="I10" t="n">
-        <v>3.09</v>
+        <v>3.0919</v>
       </c>
       <c r="J10" t="n">
-        <v>48.76</v>
+        <v>48.7645</v>
       </c>
       <c r="K10" t="n">
-        <v>48.64</v>
+        <v>48.6441</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>230829</v>
       </c>
       <c r="P10" t="n">
-        <v>97.12</v>
+        <v>97.1229</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1492,13 +1492,13 @@
         <v>22061</v>
       </c>
       <c r="I11" t="n">
-        <v>7.84</v>
+        <v>7.8354</v>
       </c>
       <c r="J11" t="n">
-        <v>49.01</v>
+        <v>49.0139</v>
       </c>
       <c r="K11" t="n">
-        <v>48.31</v>
+        <v>48.3148</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>246827</v>
       </c>
       <c r="P11" t="n">
-        <v>95.12</v>
+        <v>95.1178</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1560,13 +1560,13 @@
         <v>32399</v>
       </c>
       <c r="I12" t="n">
-        <v>12.76</v>
+        <v>12.7627</v>
       </c>
       <c r="J12" t="n">
-        <v>50.78</v>
+        <v>50.7752</v>
       </c>
       <c r="K12" t="n">
-        <v>50.46</v>
+        <v>50.4577</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>202607</v>
       </c>
       <c r="P12" t="n">
-        <v>91.48999999999999</v>
+        <v>91.48820000000001</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1628,13 +1628,13 @@
         <v>23325</v>
       </c>
       <c r="I13" t="n">
-        <v>8.710000000000001</v>
+        <v>8.714499999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>49.45</v>
+        <v>49.4538</v>
       </c>
       <c r="K13" t="n">
-        <v>49.29</v>
+        <v>49.2868</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>232466</v>
       </c>
       <c r="P13" t="n">
-        <v>95.14</v>
+        <v>95.1439</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1696,13 +1696,13 @@
         <v>16591</v>
       </c>
       <c r="I14" t="n">
-        <v>6.34</v>
+        <v>6.3359</v>
       </c>
       <c r="J14" t="n">
-        <v>49.13</v>
+        <v>49.1322</v>
       </c>
       <c r="K14" t="n">
-        <v>48.58</v>
+        <v>48.5844</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>235953</v>
       </c>
       <c r="P14" t="n">
-        <v>96.2</v>
+        <v>96.2037</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1764,13 +1764,13 @@
         <v>25775</v>
       </c>
       <c r="I15" t="n">
-        <v>11.73</v>
+        <v>11.7301</v>
       </c>
       <c r="J15" t="n">
-        <v>50.82</v>
+        <v>50.8249</v>
       </c>
       <c r="K15" t="n">
-        <v>50.37</v>
+        <v>50.3692</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>176753</v>
       </c>
       <c r="P15" t="n">
-        <v>91.13</v>
+        <v>91.12949999999999</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1832,13 +1832,13 @@
         <v>10859</v>
       </c>
       <c r="I16" t="n">
-        <v>4.04</v>
+        <v>4.037</v>
       </c>
       <c r="J16" t="n">
-        <v>48.81</v>
+        <v>48.8122</v>
       </c>
       <c r="K16" t="n">
-        <v>48.4</v>
+        <v>48.3967</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>248496</v>
       </c>
       <c r="P16" t="n">
-        <v>96.27</v>
+        <v>96.2689</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1900,13 +1900,13 @@
         <v>13422</v>
       </c>
       <c r="I17" t="n">
-        <v>4.94</v>
+        <v>4.9352</v>
       </c>
       <c r="J17" t="n">
-        <v>48.54</v>
+        <v>48.5397</v>
       </c>
       <c r="K17" t="n">
-        <v>48.26</v>
+        <v>48.2608</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>251447</v>
       </c>
       <c r="P17" t="n">
-        <v>97.25</v>
+        <v>97.2546</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1968,13 +1968,13 @@
         <v>17563</v>
       </c>
       <c r="I18" t="n">
-        <v>6.55</v>
+        <v>6.5547</v>
       </c>
       <c r="J18" t="n">
-        <v>49.85</v>
+        <v>49.8544</v>
       </c>
       <c r="K18" t="n">
-        <v>49.45</v>
+        <v>49.451</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>237856</v>
       </c>
       <c r="P18" t="n">
-        <v>95</v>
+        <v>94.99760000000001</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>24472</v>
       </c>
       <c r="I19" t="n">
-        <v>9.59</v>
+        <v>9.5868</v>
       </c>
       <c r="J19" t="n">
-        <v>48.72</v>
+        <v>48.718</v>
       </c>
       <c r="K19" t="n">
-        <v>48.31</v>
+        <v>48.3091</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2104,13 +2104,13 @@
         <v>56400</v>
       </c>
       <c r="I20" t="n">
-        <v>17.58</v>
+        <v>17.5821</v>
       </c>
       <c r="J20" t="n">
-        <v>49.28</v>
+        <v>49.278</v>
       </c>
       <c r="K20" t="n">
-        <v>49.61</v>
+        <v>49.6081</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>251889</v>
       </c>
       <c r="P20" t="n">
-        <v>95.28</v>
+        <v>95.2754</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2172,13 +2172,13 @@
         <v>26075</v>
       </c>
       <c r="I21" t="n">
-        <v>9.890000000000001</v>
+        <v>9.894600000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>50.2</v>
+        <v>50.1979</v>
       </c>
       <c r="K21" t="n">
-        <v>49.92</v>
+        <v>49.9158</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>224453</v>
       </c>
       <c r="P21" t="n">
-        <v>94.53</v>
+        <v>94.5256</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>23227</v>
       </c>
       <c r="I22" t="n">
-        <v>9.539999999999999</v>
+        <v>9.5449</v>
       </c>
       <c r="J22" t="n">
-        <v>51.36</v>
+        <v>51.3584</v>
       </c>
       <c r="K22" t="n">
-        <v>51.01</v>
+        <v>51.0145</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>203963</v>
       </c>
       <c r="P22" t="n">
-        <v>92.66</v>
+        <v>92.66079999999999</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2308,13 +2308,13 @@
         <v>16889</v>
       </c>
       <c r="I23" t="n">
-        <v>7.73</v>
+        <v>7.7292</v>
       </c>
       <c r="J23" t="n">
-        <v>50.66</v>
+        <v>50.665</v>
       </c>
       <c r="K23" t="n">
-        <v>49.98</v>
+        <v>49.9819</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>169477</v>
       </c>
       <c r="P23" t="n">
-        <v>84.06</v>
+        <v>84.0581</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2376,13 +2376,13 @@
         <v>39132</v>
       </c>
       <c r="I24" t="n">
-        <v>15.85</v>
+        <v>15.8527</v>
       </c>
       <c r="J24" t="n">
-        <v>50.82</v>
+        <v>50.8155</v>
       </c>
       <c r="K24" t="n">
-        <v>50.4</v>
+        <v>50.3962</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>173807</v>
       </c>
       <c r="P24" t="n">
-        <v>83.68000000000001</v>
+        <v>83.67529999999999</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2444,13 +2444,13 @@
         <v>23079</v>
       </c>
       <c r="I25" t="n">
-        <v>9.65</v>
+        <v>9.6472</v>
       </c>
       <c r="J25" t="n">
-        <v>51.24</v>
+        <v>51.2363</v>
       </c>
       <c r="K25" t="n">
-        <v>50.95</v>
+        <v>50.9526</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>181833</v>
       </c>
       <c r="P25" t="n">
-        <v>84.12</v>
+        <v>84.12269999999999</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2512,13 +2512,13 @@
         <v>37812</v>
       </c>
       <c r="I26" t="n">
-        <v>12.35</v>
+        <v>12.3451</v>
       </c>
       <c r="J26" t="n">
-        <v>50.25</v>
+        <v>50.2517</v>
       </c>
       <c r="K26" t="n">
-        <v>50.25</v>
+        <v>50.2481</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>250985</v>
       </c>
       <c r="P26" t="n">
-        <v>93.48</v>
+        <v>93.4837</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2580,13 +2580,13 @@
         <v>37996</v>
       </c>
       <c r="I27" t="n">
-        <v>15.91</v>
+        <v>15.9129</v>
       </c>
       <c r="J27" t="n">
         <v>49.55</v>
       </c>
       <c r="K27" t="n">
-        <v>50.23</v>
+        <v>50.2264</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>183573</v>
       </c>
       <c r="P27" t="n">
-        <v>91.43000000000001</v>
+        <v>91.43040000000001</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2648,13 +2648,13 @@
         <v>35274</v>
       </c>
       <c r="I28" t="n">
-        <v>13.97</v>
+        <v>13.9659</v>
       </c>
       <c r="J28" t="n">
-        <v>49.56</v>
+        <v>49.5566</v>
       </c>
       <c r="K28" t="n">
-        <v>49.6</v>
+        <v>49.595</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>207732</v>
       </c>
       <c r="P28" t="n">
-        <v>95.59999999999999</v>
+        <v>95.59780000000001</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2716,13 +2716,13 @@
         <v>44282</v>
       </c>
       <c r="I29" t="n">
-        <v>16.8</v>
+        <v>16.8042</v>
       </c>
       <c r="J29" t="n">
-        <v>47.53</v>
+        <v>47.5319</v>
       </c>
       <c r="K29" t="n">
-        <v>45.22</v>
+        <v>45.2207</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>211163</v>
       </c>
       <c r="P29" t="n">
-        <v>96.31999999999999</v>
+        <v>96.3177</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2784,13 +2784,13 @@
         <v>33200</v>
       </c>
       <c r="I30" t="n">
-        <v>14.1</v>
+        <v>14.1026</v>
       </c>
       <c r="J30" t="n">
-        <v>48.09</v>
+        <v>48.0857</v>
       </c>
       <c r="K30" t="n">
-        <v>46.64</v>
+        <v>46.642</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>185961</v>
       </c>
       <c r="P30" t="n">
-        <v>91.95999999999999</v>
+        <v>91.9611</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2852,13 +2852,13 @@
         <v>46816</v>
       </c>
       <c r="I31" t="n">
-        <v>19.01</v>
+        <v>19.0089</v>
       </c>
       <c r="J31" t="n">
-        <v>48.28</v>
+        <v>48.2788</v>
       </c>
       <c r="K31" t="n">
-        <v>46.2</v>
+        <v>46.1999</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>183176</v>
       </c>
       <c r="P31" t="n">
-        <v>91.83</v>
+        <v>91.8323</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2920,13 +2920,13 @@
         <v>32922</v>
       </c>
       <c r="I32" t="n">
-        <v>13.22</v>
+        <v>13.2208</v>
       </c>
       <c r="J32" t="n">
-        <v>48.4</v>
+        <v>48.4035</v>
       </c>
       <c r="K32" t="n">
-        <v>46.88</v>
+        <v>46.8826</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>199125</v>
       </c>
       <c r="P32" t="n">
-        <v>92.15000000000001</v>
+        <v>92.14700000000001</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2988,13 +2988,13 @@
         <v>46923</v>
       </c>
       <c r="I33" t="n">
-        <v>16.85</v>
+        <v>16.8471</v>
       </c>
       <c r="J33" t="n">
-        <v>48.13</v>
+        <v>48.1344</v>
       </c>
       <c r="K33" t="n">
-        <v>47.49</v>
+        <v>47.4851</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>219973</v>
       </c>
       <c r="P33" t="n">
-        <v>94.98</v>
+        <v>94.98009999999999</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         <v>33018</v>
       </c>
       <c r="I34" t="n">
-        <v>11.81</v>
+        <v>11.8112</v>
       </c>
       <c r="J34" t="n">
-        <v>47.82</v>
+        <v>47.8175</v>
       </c>
       <c r="K34" t="n">
-        <v>46.89</v>
+        <v>46.8856</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>239372</v>
       </c>
       <c r="P34" t="n">
-        <v>97.09999999999999</v>
+        <v>97.09650000000001</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -3124,13 +3124,13 @@
         <v>26396</v>
       </c>
       <c r="I35" t="n">
-        <v>8.960000000000001</v>
+        <v>8.957599999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>48.35</v>
+        <v>48.3479</v>
       </c>
       <c r="K35" t="n">
-        <v>47.66</v>
+        <v>47.6616</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>258225</v>
       </c>
       <c r="P35" t="n">
-        <v>96.25</v>
+        <v>96.2517</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -3192,13 +3192,13 @@
         <v>32654</v>
       </c>
       <c r="I36" t="n">
-        <v>15.79</v>
+        <v>15.7917</v>
       </c>
       <c r="J36" t="n">
-        <v>49.56</v>
+        <v>49.557</v>
       </c>
       <c r="K36" t="n">
-        <v>49.73</v>
+        <v>49.7347</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>164804</v>
       </c>
       <c r="P36" t="n">
-        <v>94.65000000000001</v>
+        <v>94.6464</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -3260,13 +3260,13 @@
         <v>29410</v>
       </c>
       <c r="I37" t="n">
-        <v>12.21</v>
+        <v>12.2118</v>
       </c>
       <c r="J37" t="n">
-        <v>48.68</v>
+        <v>48.6817</v>
       </c>
       <c r="K37" t="n">
-        <v>47.74</v>
+        <v>47.7382</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>204159</v>
       </c>
       <c r="P37" t="n">
-        <v>96.56</v>
+        <v>96.5647</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -3328,13 +3328,13 @@
         <v>23876</v>
       </c>
       <c r="I38" t="n">
-        <v>10.39</v>
+        <v>10.3925</v>
       </c>
       <c r="J38" t="n">
-        <v>48.09</v>
+        <v>48.0876</v>
       </c>
       <c r="K38" t="n">
-        <v>47.39</v>
+        <v>47.3864</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>199526</v>
       </c>
       <c r="P38" t="n">
-        <v>96.92</v>
+        <v>96.9199</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -3396,13 +3396,13 @@
         <v>30194</v>
       </c>
       <c r="I39" t="n">
-        <v>14.34</v>
+        <v>14.3386</v>
       </c>
       <c r="J39" t="n">
-        <v>48.5</v>
+        <v>48.4963</v>
       </c>
       <c r="K39" t="n">
-        <v>48.23</v>
+        <v>48.2346</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>173869</v>
       </c>
       <c r="P39" t="n">
-        <v>96.39</v>
+        <v>96.3877</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -3464,13 +3464,13 @@
         <v>19095</v>
       </c>
       <c r="I40" t="n">
-        <v>10.27</v>
+        <v>10.2657</v>
       </c>
       <c r="J40" t="n">
-        <v>49.76</v>
+        <v>49.7551</v>
       </c>
       <c r="K40" t="n">
-        <v>49.54</v>
+        <v>49.5369</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>158296</v>
       </c>
       <c r="P40" t="n">
-        <v>94.84</v>
+        <v>94.83799999999999</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3532,13 +3532,13 @@
         <v>32645</v>
       </c>
       <c r="I41" t="n">
-        <v>14.35</v>
+        <v>14.3457</v>
       </c>
       <c r="J41" t="n">
-        <v>49.16</v>
+        <v>49.1556</v>
       </c>
       <c r="K41" t="n">
-        <v>48.96</v>
+        <v>48.958</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>186702</v>
       </c>
       <c r="P41" t="n">
-        <v>95.79000000000001</v>
+        <v>95.7869</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3600,13 +3600,13 @@
         <v>30351</v>
       </c>
       <c r="I42" t="n">
-        <v>13.17</v>
+        <v>13.1676</v>
       </c>
       <c r="J42" t="n">
-        <v>48.75</v>
+        <v>48.7464</v>
       </c>
       <c r="K42" t="n">
-        <v>48.12</v>
+        <v>48.1239</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>192823</v>
       </c>
       <c r="P42" t="n">
-        <v>96.34</v>
+        <v>96.3412</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -3668,13 +3668,13 @@
         <v>25454</v>
       </c>
       <c r="I43" t="n">
-        <v>10.75</v>
+        <v>10.7515</v>
       </c>
       <c r="J43" t="n">
-        <v>49.45</v>
+        <v>49.4452</v>
       </c>
       <c r="K43" t="n">
-        <v>48.46</v>
+        <v>48.464</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>204074</v>
       </c>
       <c r="P43" t="n">
-        <v>96.58</v>
+        <v>96.5825</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3736,13 +3736,13 @@
         <v>19998</v>
       </c>
       <c r="I44" t="n">
-        <v>7.74</v>
+        <v>7.7443</v>
       </c>
       <c r="J44" t="n">
-        <v>49.79</v>
+        <v>49.7917</v>
       </c>
       <c r="K44" t="n">
-        <v>49.25</v>
+        <v>49.2545</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>227613</v>
       </c>
       <c r="P44" t="n">
-        <v>95.54000000000001</v>
+        <v>95.54340000000001</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3804,13 +3804,13 @@
         <v>24138</v>
       </c>
       <c r="I45" t="n">
-        <v>8.640000000000001</v>
+        <v>8.6447</v>
       </c>
       <c r="J45" t="n">
-        <v>49.7</v>
+        <v>49.7004</v>
       </c>
       <c r="K45" t="n">
-        <v>49.09</v>
+        <v>49.0907</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>243885</v>
       </c>
       <c r="P45" t="n">
-        <v>95.61</v>
+        <v>95.6093</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3872,13 +3872,13 @@
         <v>13557</v>
       </c>
       <c r="I46" t="n">
-        <v>5.25</v>
+        <v>5.255</v>
       </c>
       <c r="J46" t="n">
-        <v>48.96</v>
+        <v>48.9587</v>
       </c>
       <c r="K46" t="n">
-        <v>48.1</v>
+        <v>48.096</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>234409</v>
       </c>
       <c r="P46" t="n">
-        <v>95.90000000000001</v>
+        <v>95.901</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3940,13 +3940,13 @@
         <v>29446</v>
       </c>
       <c r="I47" t="n">
-        <v>10.98</v>
+        <v>10.9752</v>
       </c>
       <c r="J47" t="n">
-        <v>48.6</v>
+        <v>48.5997</v>
       </c>
       <c r="K47" t="n">
-        <v>47.23</v>
+        <v>47.2338</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>227099</v>
       </c>
       <c r="P47" t="n">
-        <v>95.08</v>
+        <v>95.0802</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4008,13 +4008,13 @@
         <v>34499</v>
       </c>
       <c r="I48" t="n">
-        <v>13.96</v>
+        <v>13.9565</v>
       </c>
       <c r="J48" t="n">
-        <v>49.18</v>
+        <v>49.1763</v>
       </c>
       <c r="K48" t="n">
-        <v>46.62</v>
+        <v>46.6207</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>202035</v>
       </c>
       <c r="P48" t="n">
-        <v>94.98999999999999</v>
+        <v>94.98990000000001</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4076,13 +4076,13 @@
         <v>47831</v>
       </c>
       <c r="I49" t="n">
-        <v>16.25</v>
+        <v>16.2482</v>
       </c>
       <c r="J49" t="n">
-        <v>48.42</v>
+        <v>48.417</v>
       </c>
       <c r="K49" t="n">
-        <v>47.22</v>
+        <v>47.2174</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>233138</v>
       </c>
       <c r="P49" t="n">
-        <v>94.56</v>
+        <v>94.5613</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4144,13 +4144,13 @@
         <v>31127</v>
       </c>
       <c r="I50" t="n">
-        <v>11.66</v>
+        <v>11.6628</v>
       </c>
       <c r="J50" t="n">
-        <v>48.2</v>
+        <v>48.1974</v>
       </c>
       <c r="K50" t="n">
-        <v>47.09</v>
+        <v>47.091</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>225363</v>
       </c>
       <c r="P50" t="n">
-        <v>95.59</v>
+        <v>95.58799999999999</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -4212,13 +4212,13 @@
         <v>25387</v>
       </c>
       <c r="I51" t="n">
-        <v>9.890000000000001</v>
+        <v>9.888400000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>49.74</v>
+        <v>49.7396</v>
       </c>
       <c r="K51" t="n">
-        <v>49.42</v>
+        <v>49.4238</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>220797</v>
       </c>
       <c r="P51" t="n">
-        <v>95.44</v>
+        <v>95.4393</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4280,13 +4280,13 @@
         <v>38734</v>
       </c>
       <c r="I52" t="n">
-        <v>13.46</v>
+        <v>13.4553</v>
       </c>
       <c r="J52" t="n">
-        <v>50.25</v>
+        <v>50.2461</v>
       </c>
       <c r="K52" t="n">
-        <v>50.24</v>
+        <v>50.2418</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>234560</v>
       </c>
       <c r="P52" t="n">
-        <v>94.15000000000001</v>
+        <v>94.149</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -4348,13 +4348,13 @@
         <v>39252</v>
       </c>
       <c r="I53" t="n">
-        <v>18.82</v>
+        <v>18.817</v>
       </c>
       <c r="J53" t="n">
-        <v>49.46</v>
+        <v>49.4638</v>
       </c>
       <c r="K53" t="n">
-        <v>48.82</v>
+        <v>48.8234</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>162178</v>
       </c>
       <c r="P53" t="n">
-        <v>95.77</v>
+        <v>95.7667</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -4416,13 +4416,13 @@
         <v>31534</v>
       </c>
       <c r="I54" t="n">
-        <v>11.77</v>
+        <v>11.7674</v>
       </c>
       <c r="J54" t="n">
-        <v>49.51</v>
+        <v>49.5061</v>
       </c>
       <c r="K54" t="n">
-        <v>48.94</v>
+        <v>48.9365</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>227125</v>
       </c>
       <c r="P54" t="n">
-        <v>96.06</v>
+        <v>96.0591</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -4484,13 +4484,13 @@
         <v>31891</v>
       </c>
       <c r="I55" t="n">
-        <v>12</v>
+        <v>12.0001</v>
       </c>
       <c r="J55" t="n">
-        <v>48.79</v>
+        <v>48.7936</v>
       </c>
       <c r="K55" t="n">
-        <v>47.97</v>
+        <v>47.9653</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>224839</v>
       </c>
       <c r="P55" t="n">
-        <v>96.14</v>
+        <v>96.1405</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -4552,13 +4552,13 @@
         <v>55060</v>
       </c>
       <c r="I56" t="n">
-        <v>23.26</v>
+        <v>23.2596</v>
       </c>
       <c r="J56" t="n">
-        <v>49.65</v>
+        <v>49.653</v>
       </c>
       <c r="K56" t="n">
-        <v>48.71</v>
+        <v>48.7094</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>174841</v>
       </c>
       <c r="P56" t="n">
-        <v>96.25</v>
+        <v>96.24679999999999</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -4620,13 +4620,13 @@
         <v>86910</v>
       </c>
       <c r="I57" t="n">
-        <v>35</v>
+        <v>34.9957</v>
       </c>
       <c r="J57" t="n">
-        <v>50.84</v>
+        <v>50.8373</v>
       </c>
       <c r="K57" t="n">
-        <v>51.68</v>
+        <v>51.6802</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>155430</v>
       </c>
       <c r="P57" t="n">
-        <v>96.28</v>
+        <v>96.28019999999999</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -4688,13 +4688,13 @@
         <v>48939</v>
       </c>
       <c r="I58" t="n">
-        <v>17.59</v>
+        <v>17.5947</v>
       </c>
       <c r="J58" t="n">
-        <v>49.71</v>
+        <v>49.7118</v>
       </c>
       <c r="K58" t="n">
-        <v>47.06</v>
+        <v>47.0551</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>220852</v>
       </c>
       <c r="P58" t="n">
-        <v>96.34999999999999</v>
+        <v>96.3544</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -4756,13 +4756,13 @@
         <v>44027</v>
       </c>
       <c r="I59" t="n">
-        <v>16.62</v>
+        <v>16.6211</v>
       </c>
       <c r="J59" t="n">
-        <v>49.15</v>
+        <v>49.1498</v>
       </c>
       <c r="K59" t="n">
-        <v>48.83</v>
+        <v>48.8302</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>212606</v>
       </c>
       <c r="P59" t="n">
-        <v>96.26000000000001</v>
+        <v>96.2632</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -4824,13 +4824,13 @@
         <v>62063</v>
       </c>
       <c r="I60" t="n">
-        <v>23.64</v>
+        <v>23.6417</v>
       </c>
       <c r="J60" t="n">
-        <v>48.88</v>
+        <v>48.881</v>
       </c>
       <c r="K60" t="n">
-        <v>48.16</v>
+        <v>48.1617</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>194765</v>
       </c>
       <c r="P60" t="n">
-        <v>97.16</v>
+        <v>97.16289999999999</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4892,13 +4892,13 @@
         <v>29724</v>
       </c>
       <c r="I61" t="n">
-        <v>12.05</v>
+        <v>12.0486</v>
       </c>
       <c r="J61" t="n">
-        <v>49.25</v>
+        <v>49.2467</v>
       </c>
       <c r="K61" t="n">
-        <v>47.7</v>
+        <v>47.7046</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>207660</v>
       </c>
       <c r="P61" t="n">
-        <v>95.70999999999999</v>
+        <v>95.706</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4960,13 +4960,13 @@
         <v>62771</v>
       </c>
       <c r="I62" t="n">
-        <v>25.21</v>
+        <v>25.214</v>
       </c>
       <c r="J62" t="n">
-        <v>48.96</v>
+        <v>48.9635</v>
       </c>
       <c r="K62" t="n">
-        <v>49.34</v>
+        <v>49.3431</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>180167</v>
       </c>
       <c r="P62" t="n">
-        <v>96.77</v>
+        <v>96.7693</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -5028,13 +5028,13 @@
         <v>52692</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>19.0011</v>
       </c>
       <c r="J63" t="n">
-        <v>48.67</v>
+        <v>48.6683</v>
       </c>
       <c r="K63" t="n">
-        <v>48.95</v>
+        <v>48.9533</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>218216</v>
       </c>
       <c r="P63" t="n">
-        <v>97.15000000000001</v>
+        <v>97.1498</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -5096,13 +5096,13 @@
         <v>22884</v>
       </c>
       <c r="I64" t="n">
-        <v>8.56</v>
+        <v>8.561999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>49.01</v>
+        <v>49.0076</v>
       </c>
       <c r="K64" t="n">
-        <v>48.24</v>
+        <v>48.2399</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>237202</v>
       </c>
       <c r="P64" t="n">
-        <v>97.06</v>
+        <v>97.05840000000001</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -5164,13 +5164,13 @@
         <v>30241</v>
       </c>
       <c r="I65" t="n">
-        <v>10.86</v>
+        <v>10.8581</v>
       </c>
       <c r="J65" t="n">
-        <v>49.72</v>
+        <v>49.7246</v>
       </c>
       <c r="K65" t="n">
-        <v>49.1</v>
+        <v>49.0984</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>237534</v>
       </c>
       <c r="P65" t="n">
-        <v>95.68000000000001</v>
+        <v>95.67610000000001</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -5232,13 +5232,13 @@
         <v>19678</v>
       </c>
       <c r="I66" t="n">
-        <v>7.49</v>
+        <v>7.4906</v>
       </c>
       <c r="J66" t="n">
         <v>49.43</v>
       </c>
       <c r="K66" t="n">
-        <v>48.84</v>
+        <v>48.8415</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>221580</v>
       </c>
       <c r="P66" t="n">
-        <v>91.18000000000001</v>
+        <v>91.1758</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -5300,13 +5300,13 @@
         <v>10991</v>
       </c>
       <c r="I67" t="n">
-        <v>4.55</v>
+        <v>4.552</v>
       </c>
       <c r="J67" t="n">
-        <v>48.9</v>
+        <v>48.8952</v>
       </c>
       <c r="K67" t="n">
-        <v>47.9</v>
+        <v>47.8986</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>204477</v>
       </c>
       <c r="P67" t="n">
-        <v>88.72</v>
+        <v>88.72410000000001</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -5368,13 +5368,13 @@
         <v>11226</v>
       </c>
       <c r="I68" t="n">
-        <v>4.98</v>
+        <v>4.9843</v>
       </c>
       <c r="J68" t="n">
-        <v>48.78</v>
+        <v>48.7766</v>
       </c>
       <c r="K68" t="n">
-        <v>47.84</v>
+        <v>47.8433</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>188917</v>
       </c>
       <c r="P68" t="n">
-        <v>88.28</v>
+        <v>88.2777</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
         <v>16515</v>
       </c>
       <c r="I69" t="n">
-        <v>6.62</v>
+        <v>6.6182</v>
       </c>
       <c r="J69" t="n">
-        <v>49.19</v>
+        <v>49.1903</v>
       </c>
       <c r="K69" t="n">
-        <v>48.35</v>
+        <v>48.3534</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>199460</v>
       </c>
       <c r="P69" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5963</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -5504,13 +5504,13 @@
         <v>11811</v>
       </c>
       <c r="I70" t="n">
-        <v>4.71</v>
+        <v>4.7057</v>
       </c>
       <c r="J70" t="n">
-        <v>48.69</v>
+        <v>48.6866</v>
       </c>
       <c r="K70" t="n">
-        <v>47.87</v>
+        <v>47.8744</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>214424</v>
       </c>
       <c r="P70" t="n">
-        <v>89.65000000000001</v>
+        <v>89.6481</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -5572,13 +5572,13 @@
         <v>14160</v>
       </c>
       <c r="I71" t="n">
-        <v>5.24</v>
+        <v>5.2362</v>
       </c>
       <c r="J71" t="n">
-        <v>48.6</v>
+        <v>48.5961</v>
       </c>
       <c r="K71" t="n">
-        <v>47.8</v>
+        <v>47.7978</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>239295</v>
       </c>
       <c r="P71" t="n">
-        <v>93.38</v>
+        <v>93.3772</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>20077</v>
       </c>
       <c r="I72" t="n">
-        <v>7.6</v>
+        <v>7.6032</v>
       </c>
       <c r="J72" t="n">
-        <v>48.81</v>
+        <v>48.8141</v>
       </c>
       <c r="K72" t="n">
-        <v>47.98</v>
+        <v>47.9753</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>228591</v>
       </c>
       <c r="P72" t="n">
-        <v>93.69</v>
+        <v>93.691</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -5708,13 +5708,13 @@
         <v>26379</v>
       </c>
       <c r="I73" t="n">
-        <v>9.869999999999999</v>
+        <v>9.872</v>
       </c>
       <c r="J73" t="n">
-        <v>50.99</v>
+        <v>50.9927</v>
       </c>
       <c r="K73" t="n">
-        <v>50.69</v>
+        <v>50.6909</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>224268</v>
       </c>
       <c r="P73" t="n">
-        <v>93.12</v>
+        <v>93.1229</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -5776,13 +5776,13 @@
         <v>11821</v>
       </c>
       <c r="I74" t="n">
-        <v>4.59</v>
+        <v>4.5942</v>
       </c>
       <c r="J74" t="n">
-        <v>49.21</v>
+        <v>49.2116</v>
       </c>
       <c r="K74" t="n">
-        <v>48.43</v>
+        <v>48.4309</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>235296</v>
       </c>
       <c r="P74" t="n">
-        <v>95.84999999999999</v>
+        <v>95.8498</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -5844,13 +5844,13 @@
         <v>19881</v>
       </c>
       <c r="I75" t="n">
-        <v>7.78</v>
+        <v>7.7776</v>
       </c>
       <c r="J75" t="n">
-        <v>48.86</v>
+        <v>48.8592</v>
       </c>
       <c r="K75" t="n">
-        <v>47.89</v>
+        <v>47.8915</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>221600</v>
       </c>
       <c r="P75" t="n">
-        <v>94</v>
+        <v>94.0031</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -5912,13 +5912,13 @@
         <v>8920</v>
       </c>
       <c r="I76" t="n">
-        <v>3.23</v>
+        <v>3.2284</v>
       </c>
       <c r="J76" t="n">
-        <v>49.16</v>
+        <v>49.1574</v>
       </c>
       <c r="K76" t="n">
-        <v>48.39</v>
+        <v>48.3903</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>257790</v>
       </c>
       <c r="P76" t="n">
-        <v>96.42</v>
+        <v>96.41549999999999</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -5980,13 +5980,13 @@
         <v>9238</v>
       </c>
       <c r="I77" t="n">
-        <v>3.4</v>
+        <v>3.396</v>
       </c>
       <c r="J77" t="n">
-        <v>48.66</v>
+        <v>48.6628</v>
       </c>
       <c r="K77" t="n">
-        <v>48.19</v>
+        <v>48.1938</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>253306</v>
       </c>
       <c r="P77" t="n">
-        <v>96.39</v>
+        <v>96.3921</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -6048,13 +6048,13 @@
         <v>6534</v>
       </c>
       <c r="I78" t="n">
-        <v>2.52</v>
+        <v>2.5191</v>
       </c>
       <c r="J78" t="n">
-        <v>48.82</v>
+        <v>48.8226</v>
       </c>
       <c r="K78" t="n">
-        <v>48.37</v>
+        <v>48.3717</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>240916</v>
       </c>
       <c r="P78" t="n">
-        <v>95.28</v>
+        <v>95.2825</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -6116,13 +6116,13 @@
         <v>7984</v>
       </c>
       <c r="I79" t="n">
-        <v>3.07</v>
+        <v>3.0659</v>
       </c>
       <c r="J79" t="n">
-        <v>48.43</v>
+        <v>48.425</v>
       </c>
       <c r="K79" t="n">
-        <v>48.01</v>
+        <v>48.0068</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>233588</v>
       </c>
       <c r="P79" t="n">
-        <v>92.54000000000001</v>
+        <v>92.5354</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -6184,13 +6184,13 @@
         <v>19870</v>
       </c>
       <c r="I80" t="n">
-        <v>7.9</v>
+        <v>7.9009</v>
       </c>
       <c r="J80" t="n">
-        <v>48.04</v>
+        <v>48.0385</v>
       </c>
       <c r="K80" t="n">
-        <v>47.3</v>
+        <v>47.2986</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>214650</v>
       </c>
       <c r="P80" t="n">
-        <v>92.67</v>
+        <v>92.6733</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -6252,13 +6252,13 @@
         <v>19987</v>
       </c>
       <c r="I81" t="n">
-        <v>7.92</v>
+        <v>7.9173</v>
       </c>
       <c r="J81" t="n">
-        <v>48.37</v>
+        <v>48.3694</v>
       </c>
       <c r="K81" t="n">
-        <v>47.71</v>
+        <v>47.7093</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>219023</v>
       </c>
       <c r="P81" t="n">
-        <v>94.22</v>
+        <v>94.2197</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -6320,13 +6320,13 @@
         <v>36963</v>
       </c>
       <c r="I82" t="n">
-        <v>14.46</v>
+        <v>14.4595</v>
       </c>
       <c r="J82" t="n">
-        <v>47.99</v>
+        <v>47.9936</v>
       </c>
       <c r="K82" t="n">
-        <v>47.06</v>
+        <v>47.0638</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>205920</v>
       </c>
       <c r="P82" t="n">
-        <v>94.17</v>
+        <v>94.16970000000001</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -6388,13 +6388,13 @@
         <v>25953</v>
       </c>
       <c r="I83" t="n">
-        <v>10.06</v>
+        <v>10.0589</v>
       </c>
       <c r="J83" t="n">
-        <v>47.76</v>
+        <v>47.7598</v>
       </c>
       <c r="K83" t="n">
-        <v>46.81</v>
+        <v>46.8148</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>210762</v>
       </c>
       <c r="P83" t="n">
-        <v>90.81999999999999</v>
+        <v>90.82340000000001</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -6456,13 +6456,13 @@
         <v>29121</v>
       </c>
       <c r="I84" t="n">
-        <v>11.86</v>
+        <v>11.8582</v>
       </c>
       <c r="J84" t="n">
-        <v>49.55</v>
+        <v>49.5531</v>
       </c>
       <c r="K84" t="n">
-        <v>49.36</v>
+        <v>49.3592</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>202057</v>
       </c>
       <c r="P84" t="n">
-        <v>93.34999999999999</v>
+        <v>93.34780000000001</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -6524,13 +6524,13 @@
         <v>21054</v>
       </c>
       <c r="I85" t="n">
-        <v>8.390000000000001</v>
+        <v>8.385899999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>49.24</v>
+        <v>49.2442</v>
       </c>
       <c r="K85" t="n">
-        <v>48.62</v>
+        <v>48.6177</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>218181</v>
       </c>
       <c r="P85" t="n">
-        <v>94.86</v>
+        <v>94.85680000000001</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -6592,13 +6592,13 @@
         <v>22279</v>
       </c>
       <c r="I86" t="n">
-        <v>9.6</v>
+        <v>9.6005</v>
       </c>
       <c r="J86" t="n">
-        <v>48.34</v>
+        <v>48.3375</v>
       </c>
       <c r="K86" t="n">
-        <v>47.85</v>
+        <v>47.847</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>197084</v>
       </c>
       <c r="P86" t="n">
-        <v>93.95</v>
+        <v>93.94750000000001</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -6660,13 +6660,13 @@
         <v>30387</v>
       </c>
       <c r="I87" t="n">
-        <v>11.78</v>
+        <v>11.7841</v>
       </c>
       <c r="J87" t="n">
-        <v>48.64</v>
+        <v>48.6373</v>
       </c>
       <c r="K87" t="n">
-        <v>47.96</v>
+        <v>47.9631</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>214973</v>
       </c>
       <c r="P87" t="n">
-        <v>94.5</v>
+        <v>94.50320000000001</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -6728,13 +6728,13 @@
         <v>33851</v>
       </c>
       <c r="I88" t="n">
-        <v>12.7</v>
+        <v>12.6989</v>
       </c>
       <c r="J88" t="n">
-        <v>49.59</v>
+        <v>49.5909</v>
       </c>
       <c r="K88" t="n">
-        <v>48.79</v>
+        <v>48.7852</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>217135</v>
       </c>
       <c r="P88" t="n">
-        <v>93.3</v>
+        <v>93.3047</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -6796,13 +6796,13 @@
         <v>27601</v>
       </c>
       <c r="I89" t="n">
-        <v>9.84</v>
+        <v>9.835100000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>48.05</v>
+        <v>48.0503</v>
       </c>
       <c r="K89" t="n">
-        <v>47.63</v>
+        <v>47.6276</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>232467</v>
       </c>
       <c r="P89" t="n">
-        <v>91.87</v>
+        <v>91.8711</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -6864,13 +6864,13 @@
         <v>40310</v>
       </c>
       <c r="I90" t="n">
-        <v>14.78</v>
+        <v>14.7813</v>
       </c>
       <c r="J90" t="n">
-        <v>47.69</v>
+        <v>47.6926</v>
       </c>
       <c r="K90" t="n">
-        <v>47.34</v>
+        <v>47.3419</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>211396</v>
       </c>
       <c r="P90" t="n">
-        <v>90.95999999999999</v>
+        <v>90.96250000000001</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -6932,13 +6932,13 @@
         <v>38437</v>
       </c>
       <c r="I91" t="n">
-        <v>13.17</v>
+        <v>13.1731</v>
       </c>
       <c r="J91" t="n">
-        <v>48.99</v>
+        <v>48.9926</v>
       </c>
       <c r="K91" t="n">
-        <v>48.32</v>
+        <v>48.3244</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>232685</v>
       </c>
       <c r="P91" t="n">
-        <v>91.84</v>
+        <v>91.8447</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -7000,13 +7000,13 @@
         <v>27052</v>
       </c>
       <c r="I92" t="n">
-        <v>10.78</v>
+        <v>10.7763</v>
       </c>
       <c r="J92" t="n">
-        <v>49.07</v>
+        <v>49.0708</v>
       </c>
       <c r="K92" t="n">
-        <v>48.57</v>
+        <v>48.5738</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>210720</v>
       </c>
       <c r="P92" t="n">
-        <v>94.08</v>
+        <v>94.07940000000001</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -7068,13 +7068,13 @@
         <v>36230</v>
       </c>
       <c r="I93" t="n">
-        <v>13.58</v>
+        <v>13.5836</v>
       </c>
       <c r="J93" t="n">
         <v>49.5</v>
       </c>
       <c r="K93" t="n">
-        <v>48.9</v>
+        <v>48.8956</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>215506</v>
       </c>
       <c r="P93" t="n">
-        <v>93.5</v>
+        <v>93.4995</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -7136,13 +7136,13 @@
         <v>21682</v>
       </c>
       <c r="I94" t="n">
-        <v>8.789999999999999</v>
+        <v>8.785600000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>48.76</v>
+        <v>48.7643</v>
       </c>
       <c r="K94" t="n">
-        <v>48.04</v>
+        <v>48.0443</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>212756</v>
       </c>
       <c r="P94" t="n">
-        <v>94.51000000000001</v>
+        <v>94.5124</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -7204,13 +7204,13 @@
         <v>44520</v>
       </c>
       <c r="I95" t="n">
-        <v>15.59</v>
+        <v>15.5932</v>
       </c>
       <c r="J95" t="n">
-        <v>48.42</v>
+        <v>48.4195</v>
       </c>
       <c r="K95" t="n">
-        <v>47.62</v>
+        <v>47.615</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>217223</v>
       </c>
       <c r="P95" t="n">
-        <v>90.14</v>
+        <v>90.13809999999999</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -7272,13 +7272,13 @@
         <v>37396</v>
       </c>
       <c r="I96" t="n">
-        <v>14.2</v>
+        <v>14.1997</v>
       </c>
       <c r="J96" t="n">
-        <v>49.39</v>
+        <v>49.3932</v>
       </c>
       <c r="K96" t="n">
-        <v>48.43</v>
+        <v>48.4258</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>211344</v>
       </c>
       <c r="P96" t="n">
-        <v>93.53</v>
+        <v>93.5308</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -7340,13 +7340,13 @@
         <v>32054</v>
       </c>
       <c r="I97" t="n">
-        <v>12.31</v>
+        <v>12.3089</v>
       </c>
       <c r="J97" t="n">
-        <v>49.28</v>
+        <v>49.284</v>
       </c>
       <c r="K97" t="n">
-        <v>48.36</v>
+        <v>48.3559</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>212191</v>
       </c>
       <c r="P97" t="n">
-        <v>92.92</v>
+        <v>92.9199</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -7408,13 +7408,13 @@
         <v>39863</v>
       </c>
       <c r="I98" t="n">
-        <v>15.18</v>
+        <v>15.1809</v>
       </c>
       <c r="J98" t="n">
-        <v>49.32</v>
+        <v>49.3195</v>
       </c>
       <c r="K98" t="n">
-        <v>48.85</v>
+        <v>48.8495</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>209201</v>
       </c>
       <c r="P98" t="n">
-        <v>93.93000000000001</v>
+        <v>93.9288</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -7476,13 +7476,13 @@
         <v>22033</v>
       </c>
       <c r="I99" t="n">
-        <v>8.779999999999999</v>
+        <v>8.7782</v>
       </c>
       <c r="J99" t="n">
-        <v>48.95</v>
+        <v>48.955</v>
       </c>
       <c r="K99" t="n">
-        <v>47.83</v>
+        <v>47.8309</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>218120</v>
       </c>
       <c r="P99" t="n">
-        <v>95.26000000000001</v>
+        <v>95.26349999999999</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -7544,13 +7544,13 @@
         <v>15122</v>
       </c>
       <c r="I100" t="n">
-        <v>6.02</v>
+        <v>6.0179</v>
       </c>
       <c r="J100" t="n">
-        <v>49.15</v>
+        <v>49.1456</v>
       </c>
       <c r="K100" t="n">
-        <v>48.26</v>
+        <v>48.2597</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>227365</v>
       </c>
       <c r="P100" t="n">
-        <v>96.28</v>
+        <v>96.27500000000001</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -7612,13 +7612,13 @@
         <v>40167</v>
       </c>
       <c r="I101" t="n">
-        <v>16.13</v>
+        <v>16.132</v>
       </c>
       <c r="J101" t="n">
-        <v>49</v>
+        <v>48.9965</v>
       </c>
       <c r="K101" t="n">
-        <v>48.44</v>
+        <v>48.4413</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>198737</v>
       </c>
       <c r="P101" t="n">
-        <v>95.17</v>
+        <v>95.1705</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -7680,13 +7680,13 @@
         <v>36980</v>
       </c>
       <c r="I102" t="n">
-        <v>13.88</v>
+        <v>13.8769</v>
       </c>
       <c r="J102" t="n">
-        <v>49.83</v>
+        <v>49.8251</v>
       </c>
       <c r="K102" t="n">
-        <v>48.88</v>
+        <v>48.8811</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>219757</v>
       </c>
       <c r="P102" t="n">
-        <v>95.75</v>
+        <v>95.7522</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -7748,13 +7748,13 @@
         <v>30084</v>
       </c>
       <c r="I103" t="n">
-        <v>11.97</v>
+        <v>11.9718</v>
       </c>
       <c r="J103" t="n">
-        <v>48.63</v>
+        <v>48.6325</v>
       </c>
       <c r="K103" t="n">
-        <v>47.84</v>
+        <v>47.8389</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>213502</v>
       </c>
       <c r="P103" t="n">
-        <v>96.52</v>
+        <v>96.5168</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -7816,13 +7816,13 @@
         <v>33245</v>
       </c>
       <c r="I104" t="n">
-        <v>17.37</v>
+        <v>17.3747</v>
       </c>
       <c r="J104" t="n">
-        <v>49.25</v>
+        <v>49.2498</v>
       </c>
       <c r="K104" t="n">
-        <v>49.36</v>
+        <v>49.3574</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>144886</v>
       </c>
       <c r="P104" t="n">
-        <v>91.64</v>
+        <v>91.6443</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -7884,13 +7884,13 @@
         <v>24524</v>
       </c>
       <c r="I105" t="n">
-        <v>12.57</v>
+        <v>12.5696</v>
       </c>
       <c r="J105" t="n">
-        <v>50.38</v>
+        <v>50.378</v>
       </c>
       <c r="K105" t="n">
-        <v>49.98</v>
+        <v>49.9768</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>157664</v>
       </c>
       <c r="P105" t="n">
-        <v>92.43000000000001</v>
+        <v>92.4276</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -7952,13 +7952,13 @@
         <v>38273</v>
       </c>
       <c r="I106" t="n">
-        <v>24.62</v>
+        <v>24.6179</v>
       </c>
       <c r="J106" t="n">
-        <v>46.17</v>
+        <v>46.169</v>
       </c>
       <c r="K106" t="n">
-        <v>47.25</v>
+        <v>47.2503</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>106314</v>
       </c>
       <c r="P106" t="n">
-        <v>90.72</v>
+        <v>90.71550000000001</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -8020,13 +8020,13 @@
         <v>39554</v>
       </c>
       <c r="I107" t="n">
-        <v>16.82</v>
+        <v>16.8183</v>
       </c>
       <c r="J107" t="n">
-        <v>48.85</v>
+        <v>48.8498</v>
       </c>
       <c r="K107" t="n">
-        <v>49.06</v>
+        <v>49.0574</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>183193</v>
       </c>
       <c r="P107" t="n">
-        <v>93.64</v>
+        <v>93.6426</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -8088,13 +8088,13 @@
         <v>50874</v>
       </c>
       <c r="I108" t="n">
-        <v>19.23</v>
+        <v>19.2267</v>
       </c>
       <c r="J108" t="n">
-        <v>50.12</v>
+        <v>50.1226</v>
       </c>
       <c r="K108" t="n">
-        <v>49.89</v>
+        <v>49.8898</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>195177</v>
       </c>
       <c r="P108" t="n">
-        <v>91.31999999999999</v>
+        <v>91.3207</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -8156,13 +8156,13 @@
         <v>45092</v>
       </c>
       <c r="I109" t="n">
-        <v>20.9</v>
+        <v>20.9013</v>
       </c>
       <c r="J109" t="n">
-        <v>48.89</v>
+        <v>48.8931</v>
       </c>
       <c r="K109" t="n">
-        <v>49.55</v>
+        <v>49.5458</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>154918</v>
       </c>
       <c r="P109" t="n">
-        <v>90.78</v>
+        <v>90.7833</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -8224,13 +8224,13 @@
         <v>30542</v>
       </c>
       <c r="I110" t="n">
-        <v>12.7</v>
+        <v>12.7048</v>
       </c>
       <c r="J110" t="n">
-        <v>50.32</v>
+        <v>50.318</v>
       </c>
       <c r="K110" t="n">
-        <v>49.97</v>
+        <v>49.9664</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>196505</v>
       </c>
       <c r="P110" t="n">
-        <v>93.64</v>
+        <v>93.63849999999999</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -8292,13 +8292,13 @@
         <v>41721</v>
       </c>
       <c r="I111" t="n">
-        <v>14.79</v>
+        <v>14.7914</v>
       </c>
       <c r="J111" t="n">
-        <v>50.87</v>
+        <v>50.8736</v>
       </c>
       <c r="K111" t="n">
-        <v>50.77</v>
+        <v>50.7666</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -8360,13 +8360,13 @@
         <v>40970</v>
       </c>
       <c r="I112" t="n">
-        <v>17.76</v>
+        <v>17.7602</v>
       </c>
       <c r="J112" t="n">
-        <v>50.55</v>
+        <v>50.5523</v>
       </c>
       <c r="K112" t="n">
-        <v>50.55</v>
+        <v>50.5524</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>174984</v>
       </c>
       <c r="P112" t="n">
-        <v>92.23999999999999</v>
+        <v>92.23569999999999</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -8428,13 +8428,13 @@
         <v>39574</v>
       </c>
       <c r="I113" t="n">
-        <v>19.57</v>
+        <v>19.5698</v>
       </c>
       <c r="J113" t="n">
-        <v>49.75</v>
+        <v>49.7463</v>
       </c>
       <c r="K113" t="n">
-        <v>50.38</v>
+        <v>50.3837</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>148272</v>
       </c>
       <c r="P113" t="n">
-        <v>91.16</v>
+        <v>91.16240000000001</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -8496,13 +8496,13 @@
         <v>32401</v>
       </c>
       <c r="I114" t="n">
-        <v>14.8</v>
+        <v>14.7989</v>
       </c>
       <c r="J114" t="n">
-        <v>51.14</v>
+        <v>51.1359</v>
       </c>
       <c r="K114" t="n">
-        <v>51.38</v>
+        <v>51.3812</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>169347</v>
       </c>
       <c r="P114" t="n">
-        <v>90.78</v>
+        <v>90.78270000000001</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -8564,13 +8564,13 @@
         <v>38605</v>
       </c>
       <c r="I115" t="n">
-        <v>15.07</v>
+        <v>15.0715</v>
       </c>
       <c r="J115" t="n">
-        <v>50.98</v>
+        <v>50.9811</v>
       </c>
       <c r="K115" t="n">
-        <v>51.44</v>
+        <v>51.4423</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>198098</v>
       </c>
       <c r="P115" t="n">
-        <v>91.06</v>
+        <v>91.0624</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -8632,13 +8632,13 @@
         <v>49715</v>
       </c>
       <c r="I116" t="n">
-        <v>15.67</v>
+        <v>15.6652</v>
       </c>
       <c r="J116" t="n">
-        <v>49.24</v>
+        <v>49.2384</v>
       </c>
       <c r="K116" t="n">
-        <v>49.15</v>
+        <v>49.1476</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>252560</v>
       </c>
       <c r="P116" t="n">
-        <v>94.36</v>
+        <v>94.3638</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -8700,13 +8700,13 @@
         <v>43887</v>
       </c>
       <c r="I117" t="n">
-        <v>17.71</v>
+        <v>17.7132</v>
       </c>
       <c r="J117" t="n">
-        <v>50.94</v>
+        <v>50.9368</v>
       </c>
       <c r="K117" t="n">
-        <v>51.49</v>
+        <v>51.4913</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>177484</v>
       </c>
       <c r="P117" t="n">
-        <v>87.05</v>
+        <v>87.0544</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -8768,13 +8768,13 @@
         <v>50315</v>
       </c>
       <c r="I118" t="n">
-        <v>18.69</v>
+        <v>18.6902</v>
       </c>
       <c r="J118" t="n">
-        <v>51</v>
+        <v>51.0043</v>
       </c>
       <c r="K118" t="n">
-        <v>51.36</v>
+        <v>51.3632</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>195730</v>
       </c>
       <c r="P118" t="n">
-        <v>89.42</v>
+        <v>89.41930000000001</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -8836,13 +8836,13 @@
         <v>40211</v>
       </c>
       <c r="I119" t="n">
-        <v>14.12</v>
+        <v>14.1242</v>
       </c>
       <c r="J119" t="n">
-        <v>49.74</v>
+        <v>49.7432</v>
       </c>
       <c r="K119" t="n">
-        <v>49.34</v>
+        <v>49.3355</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>232916</v>
       </c>
       <c r="P119" t="n">
-        <v>95.27</v>
+        <v>95.268</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -8904,13 +8904,13 @@
         <v>35625</v>
       </c>
       <c r="I120" t="n">
-        <v>12.37</v>
+        <v>12.367</v>
       </c>
       <c r="J120" t="n">
-        <v>50.23</v>
+        <v>50.227</v>
       </c>
       <c r="K120" t="n">
-        <v>50.07</v>
+        <v>50.0707</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>236603</v>
       </c>
       <c r="P120" t="n">
-        <v>93.73</v>
+        <v>93.7268</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -8972,13 +8972,13 @@
         <v>12034</v>
       </c>
       <c r="I121" t="n">
-        <v>4.77</v>
+        <v>4.7746</v>
       </c>
       <c r="J121" t="n">
-        <v>48.76</v>
+        <v>48.7623</v>
       </c>
       <c r="K121" t="n">
-        <v>48.08</v>
+        <v>48.0803</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>233473</v>
       </c>
       <c r="P121" t="n">
-        <v>97.28</v>
+        <v>97.27760000000001</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -9040,13 +9040,13 @@
         <v>25561</v>
       </c>
       <c r="I122" t="n">
-        <v>9.5</v>
+        <v>9.5036</v>
       </c>
       <c r="J122" t="n">
-        <v>48.47</v>
+        <v>48.4691</v>
       </c>
       <c r="K122" t="n">
-        <v>47.61</v>
+        <v>47.6138</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>237469</v>
       </c>
       <c r="P122" t="n">
-        <v>97.56</v>
+        <v>97.5633</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -9108,13 +9108,13 @@
         <v>24471</v>
       </c>
       <c r="I123" t="n">
-        <v>9.93</v>
+        <v>9.928100000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>48.21</v>
+        <v>48.2104</v>
       </c>
       <c r="K123" t="n">
-        <v>46.23</v>
+        <v>46.2279</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>215848</v>
       </c>
       <c r="P123" t="n">
-        <v>97.22</v>
+        <v>97.224</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -9176,13 +9176,13 @@
         <v>22488</v>
       </c>
       <c r="I124" t="n">
-        <v>9.15</v>
+        <v>9.150499999999999</v>
       </c>
       <c r="J124" t="n">
-        <v>48.74</v>
+        <v>48.7372</v>
       </c>
       <c r="K124" t="n">
-        <v>47.31</v>
+        <v>47.3075</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>216180</v>
       </c>
       <c r="P124" t="n">
-        <v>96.81999999999999</v>
+        <v>96.8249</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -9244,13 +9244,13 @@
         <v>19747</v>
       </c>
       <c r="I125" t="n">
-        <v>7.05</v>
+        <v>7.0498</v>
       </c>
       <c r="J125" t="n">
-        <v>49.57</v>
+        <v>49.5655</v>
       </c>
       <c r="K125" t="n">
-        <v>49</v>
+        <v>49.0023</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>250535</v>
       </c>
       <c r="P125" t="n">
-        <v>96.23</v>
+        <v>96.226</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -9312,13 +9312,13 @@
         <v>32167</v>
       </c>
       <c r="I126" t="n">
-        <v>11.59</v>
+        <v>11.5894</v>
       </c>
       <c r="J126" t="n">
-        <v>48.68</v>
+        <v>48.6844</v>
       </c>
       <c r="K126" t="n">
-        <v>48.33</v>
+        <v>48.3349</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>238563</v>
       </c>
       <c r="P126" t="n">
-        <v>97.22</v>
+        <v>97.2187</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -9380,13 +9380,13 @@
         <v>18992</v>
       </c>
       <c r="I127" t="n">
-        <v>8.109999999999999</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>48.88</v>
+        <v>48.8762</v>
       </c>
       <c r="K127" t="n">
-        <v>47.92</v>
+        <v>47.9189</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>207071</v>
       </c>
       <c r="P127" t="n">
-        <v>96.26000000000001</v>
+        <v>96.25749999999999</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -9448,13 +9448,13 @@
         <v>15907</v>
       </c>
       <c r="I128" t="n">
-        <v>6.71</v>
+        <v>6.7051</v>
       </c>
       <c r="J128" t="n">
-        <v>48.7</v>
+        <v>48.7049</v>
       </c>
       <c r="K128" t="n">
-        <v>47.74</v>
+        <v>47.7396</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>211328</v>
       </c>
       <c r="P128" t="n">
-        <v>95.48</v>
+        <v>95.48009999999999</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -9516,13 +9516,13 @@
         <v>32962</v>
       </c>
       <c r="I129" t="n">
-        <v>12.06</v>
+        <v>12.0623</v>
       </c>
       <c r="J129" t="n">
-        <v>48.95</v>
+        <v>48.9477</v>
       </c>
       <c r="K129" t="n">
-        <v>47.57</v>
+        <v>47.5699</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>231860</v>
       </c>
       <c r="P129" t="n">
-        <v>96.48999999999999</v>
+        <v>96.48650000000001</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -9584,13 +9584,13 @@
         <v>22935</v>
       </c>
       <c r="I130" t="n">
-        <v>8.06</v>
+        <v>8.056699999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>48.61</v>
+        <v>48.6077</v>
       </c>
       <c r="K130" t="n">
-        <v>47.22</v>
+        <v>47.2197</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>253551</v>
       </c>
       <c r="P130" t="n">
-        <v>96.87</v>
+        <v>96.8728</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -9652,13 +9652,13 @@
         <v>14322</v>
       </c>
       <c r="I131" t="n">
-        <v>5.26</v>
+        <v>5.2649</v>
       </c>
       <c r="J131" t="n">
-        <v>48.11</v>
+        <v>48.109</v>
       </c>
       <c r="K131" t="n">
-        <v>47.3</v>
+        <v>47.3016</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>246059</v>
       </c>
       <c r="P131" t="n">
-        <v>95.48</v>
+        <v>95.4812</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -9720,13 +9720,13 @@
         <v>19785</v>
       </c>
       <c r="I132" t="n">
-        <v>7.57</v>
+        <v>7.5658</v>
       </c>
       <c r="J132" t="n">
-        <v>48.56</v>
+        <v>48.5601</v>
       </c>
       <c r="K132" t="n">
-        <v>47.8</v>
+        <v>47.8016</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>231303</v>
       </c>
       <c r="P132" t="n">
-        <v>95.69</v>
+        <v>95.6905</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -9788,10 +9788,10 @@
         <v>10743</v>
       </c>
       <c r="I133" t="n">
-        <v>3.77</v>
+        <v>3.7715</v>
       </c>
       <c r="J133" t="n">
-        <v>48.12</v>
+        <v>48.1155</v>
       </c>
       <c r="K133" t="n">
         <v>47.5</v>
@@ -9813,7 +9813,7 @@
         <v>258107</v>
       </c>
       <c r="P133" t="n">
-        <v>94.16</v>
+        <v>94.16419999999999</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -9856,13 +9856,13 @@
         <v>15882</v>
       </c>
       <c r="I134" t="n">
-        <v>6.83</v>
+        <v>6.8309</v>
       </c>
       <c r="J134" t="n">
-        <v>49.25</v>
+        <v>49.2508</v>
       </c>
       <c r="K134" t="n">
-        <v>47.93</v>
+        <v>47.9263</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>207706</v>
       </c>
       <c r="P134" t="n">
-        <v>95.88</v>
+        <v>95.88500000000001</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -9924,13 +9924,13 @@
         <v>19737</v>
       </c>
       <c r="I135" t="n">
-        <v>6.86</v>
+        <v>6.8631</v>
       </c>
       <c r="J135" t="n">
-        <v>48.77</v>
+        <v>48.7654</v>
       </c>
       <c r="K135" t="n">
-        <v>47.93</v>
+        <v>47.9328</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>257773</v>
       </c>
       <c r="P135" t="n">
-        <v>96.23999999999999</v>
+        <v>96.2393</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -9992,13 +9992,13 @@
         <v>17572</v>
       </c>
       <c r="I136" t="n">
-        <v>7.33</v>
+        <v>7.332</v>
       </c>
       <c r="J136" t="n">
-        <v>48.99</v>
+        <v>48.9857</v>
       </c>
       <c r="K136" t="n">
-        <v>47.96</v>
+        <v>47.9562</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>213229</v>
       </c>
       <c r="P136" t="n">
-        <v>96.01000000000001</v>
+        <v>96.0102</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -10060,13 +10060,13 @@
         <v>25182</v>
       </c>
       <c r="I137" t="n">
-        <v>9.98</v>
+        <v>9.9762</v>
       </c>
       <c r="J137" t="n">
-        <v>49.32</v>
+        <v>49.3158</v>
       </c>
       <c r="K137" t="n">
-        <v>47.84</v>
+        <v>47.8441</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>219107</v>
       </c>
       <c r="P137" t="n">
-        <v>96.42</v>
+        <v>96.4218</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -10128,13 +10128,13 @@
         <v>40301</v>
       </c>
       <c r="I138" t="n">
-        <v>14.12</v>
+        <v>14.1205</v>
       </c>
       <c r="J138" t="n">
-        <v>49.31</v>
+        <v>49.3092</v>
       </c>
       <c r="K138" t="n">
-        <v>48.29</v>
+        <v>48.2852</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>237319</v>
       </c>
       <c r="P138" t="n">
-        <v>96.81999999999999</v>
+        <v>96.82299999999999</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -10196,13 +10196,13 @@
         <v>30756</v>
       </c>
       <c r="I139" t="n">
-        <v>11.43</v>
+        <v>11.4338</v>
       </c>
       <c r="J139" t="n">
-        <v>49.26</v>
+        <v>49.2628</v>
       </c>
       <c r="K139" t="n">
-        <v>48.04</v>
+        <v>48.036</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>230686</v>
       </c>
       <c r="P139" t="n">
-        <v>96.83</v>
+        <v>96.8309</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -10264,13 +10264,13 @@
         <v>29583</v>
       </c>
       <c r="I140" t="n">
-        <v>10.71</v>
+        <v>10.7085</v>
       </c>
       <c r="J140" t="n">
-        <v>48.94</v>
+        <v>48.9434</v>
       </c>
       <c r="K140" t="n">
-        <v>47.46</v>
+        <v>47.4649</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>241664</v>
       </c>
       <c r="P140" t="n">
-        <v>97.97</v>
+        <v>97.96939999999999</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -10332,13 +10332,13 @@
         <v>42622</v>
       </c>
       <c r="I141" t="n">
-        <v>15.46</v>
+        <v>15.4585</v>
       </c>
       <c r="J141" t="n">
-        <v>50.6</v>
+        <v>50.6012</v>
       </c>
       <c r="K141" t="n">
-        <v>49.96</v>
+        <v>49.9599</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>221031</v>
       </c>
       <c r="P141" t="n">
-        <v>94.81999999999999</v>
+        <v>94.8236</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -10400,13 +10400,13 @@
         <v>19348</v>
       </c>
       <c r="I142" t="n">
-        <v>7.68</v>
+        <v>7.6797</v>
       </c>
       <c r="J142" t="n">
-        <v>48.94</v>
+        <v>48.942</v>
       </c>
       <c r="K142" t="n">
-        <v>47.22</v>
+        <v>47.215</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>222178</v>
       </c>
       <c r="P142" t="n">
-        <v>95.52</v>
+        <v>95.5239</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
@@ -10468,13 +10468,13 @@
         <v>21922</v>
       </c>
       <c r="I143" t="n">
-        <v>9.17</v>
+        <v>9.1745</v>
       </c>
       <c r="J143" t="n">
-        <v>48.71</v>
+        <v>48.7097</v>
       </c>
       <c r="K143" t="n">
-        <v>47.49</v>
+        <v>47.4947</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>205362</v>
       </c>
       <c r="P143" t="n">
-        <v>94.63</v>
+        <v>94.62730000000001</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -10536,13 +10536,13 @@
         <v>19955</v>
       </c>
       <c r="I144" t="n">
-        <v>7.53</v>
+        <v>7.5287</v>
       </c>
       <c r="J144" t="n">
-        <v>49.49</v>
+        <v>49.4854</v>
       </c>
       <c r="K144" t="n">
-        <v>48.77</v>
+        <v>48.7729</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>232238</v>
       </c>
       <c r="P144" t="n">
-        <v>94.75</v>
+        <v>94.7535</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -10604,13 +10604,13 @@
         <v>8738</v>
       </c>
       <c r="I145" t="n">
-        <v>3.56</v>
+        <v>3.5639</v>
       </c>
       <c r="J145" t="n">
-        <v>49.24</v>
+        <v>49.2373</v>
       </c>
       <c r="K145" t="n">
-        <v>48.69</v>
+        <v>48.6944</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>210192</v>
       </c>
       <c r="P145" t="n">
-        <v>88.90000000000001</v>
+        <v>88.8972</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -10672,13 +10672,13 @@
         <v>22511</v>
       </c>
       <c r="I146" t="n">
-        <v>8.08</v>
+        <v>8.0753</v>
       </c>
       <c r="J146" t="n">
-        <v>49.54</v>
+        <v>49.5419</v>
       </c>
       <c r="K146" t="n">
-        <v>48.48</v>
+        <v>48.4759</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>239370</v>
       </c>
       <c r="P146" t="n">
-        <v>93.41</v>
+        <v>93.4123</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -10740,13 +10740,13 @@
         <v>22864</v>
       </c>
       <c r="I147" t="n">
-        <v>7.85</v>
+        <v>7.8535</v>
       </c>
       <c r="J147" t="n">
-        <v>49.63</v>
+        <v>49.6301</v>
       </c>
       <c r="K147" t="n">
-        <v>48.65</v>
+        <v>48.6502</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>250592</v>
       </c>
       <c r="P147" t="n">
-        <v>93.41</v>
+        <v>93.4118</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -10808,13 +10808,13 @@
         <v>37611</v>
       </c>
       <c r="I148" t="n">
-        <v>12.6</v>
+        <v>12.5956</v>
       </c>
       <c r="J148" t="n">
-        <v>50.91</v>
+        <v>50.9106</v>
       </c>
       <c r="K148" t="n">
-        <v>50.58</v>
+        <v>50.5822</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>246393</v>
       </c>
       <c r="P148" t="n">
-        <v>94.41</v>
+        <v>94.40600000000001</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -10876,13 +10876,13 @@
         <v>14582</v>
       </c>
       <c r="I149" t="n">
-        <v>5.08</v>
+        <v>5.0757</v>
       </c>
       <c r="J149" t="n">
-        <v>48.73</v>
+        <v>48.7252</v>
       </c>
       <c r="K149" t="n">
-        <v>47.68</v>
+        <v>47.6754</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>267394</v>
       </c>
       <c r="P149" t="n">
-        <v>98.05</v>
+        <v>98.05029999999999</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -10944,13 +10944,13 @@
         <v>52197</v>
       </c>
       <c r="I150" t="n">
-        <v>16.42</v>
+        <v>16.4238</v>
       </c>
       <c r="J150" t="n">
-        <v>49.62</v>
+        <v>49.6188</v>
       </c>
       <c r="K150" t="n">
-        <v>50.51</v>
+        <v>50.5083</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -11012,13 +11012,13 @@
         <v>45788</v>
       </c>
       <c r="I151" t="n">
-        <v>14.93</v>
+        <v>14.9337</v>
       </c>
       <c r="J151" t="n">
-        <v>51.8</v>
+        <v>51.8041</v>
       </c>
       <c r="K151" t="n">
-        <v>52.25</v>
+        <v>52.2535</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>231075</v>
       </c>
       <c r="P151" t="n">
-        <v>88.59999999999999</v>
+        <v>88.59520000000001</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -11080,13 +11080,13 @@
         <v>43272</v>
       </c>
       <c r="I152" t="n">
-        <v>13.67</v>
+        <v>13.6724</v>
       </c>
       <c r="J152" t="n">
-        <v>50.45</v>
+        <v>50.4491</v>
       </c>
       <c r="K152" t="n">
-        <v>50.34</v>
+        <v>50.3387</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>256444</v>
       </c>
       <c r="P152" t="n">
-        <v>93.86</v>
+        <v>93.86020000000001</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
@@ -11148,13 +11148,13 @@
         <v>33408</v>
       </c>
       <c r="I153" t="n">
-        <v>12.68</v>
+        <v>12.6833</v>
       </c>
       <c r="J153" t="n">
-        <v>51.58</v>
+        <v>51.5831</v>
       </c>
       <c r="K153" t="n">
-        <v>51.88</v>
+        <v>51.8809</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>205661</v>
       </c>
       <c r="P153" t="n">
-        <v>89.42</v>
+        <v>89.42019999999999</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
@@ -11216,13 +11216,13 @@
         <v>53794</v>
       </c>
       <c r="I154" t="n">
-        <v>17.16</v>
+        <v>17.1567</v>
       </c>
       <c r="J154" t="n">
-        <v>51.05</v>
+        <v>51.0455</v>
       </c>
       <c r="K154" t="n">
-        <v>51.49</v>
+        <v>51.4856</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>234687</v>
       </c>
       <c r="P154" t="n">
-        <v>90.34999999999999</v>
+        <v>90.35039999999999</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -11284,13 +11284,13 @@
         <v>51936</v>
       </c>
       <c r="I155" t="n">
-        <v>16.33</v>
+        <v>16.3265</v>
       </c>
       <c r="J155" t="n">
-        <v>51.44</v>
+        <v>51.4352</v>
       </c>
       <c r="K155" t="n">
-        <v>51.68</v>
+        <v>51.6814</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>238796</v>
       </c>
       <c r="P155" t="n">
-        <v>89.70999999999999</v>
+        <v>89.7146</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>33908</v>
       </c>
       <c r="I156" t="n">
-        <v>12.23</v>
+        <v>12.2291</v>
       </c>
       <c r="J156" t="n">
-        <v>49.98</v>
+        <v>49.9836</v>
       </c>
       <c r="K156" t="n">
-        <v>49.47</v>
+        <v>49.4689</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>229791</v>
       </c>
       <c r="P156" t="n">
-        <v>94.42</v>
+        <v>94.4224</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -11420,13 +11420,13 @@
         <v>31712</v>
       </c>
       <c r="I157" t="n">
-        <v>12.12</v>
+        <v>12.1214</v>
       </c>
       <c r="J157" t="n">
-        <v>49.56</v>
+        <v>49.5648</v>
       </c>
       <c r="K157" t="n">
-        <v>48.93</v>
+        <v>48.9307</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>218093</v>
       </c>
       <c r="P157" t="n">
-        <v>94.86</v>
+        <v>94.8614</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -11488,13 +11488,13 @@
         <v>72267</v>
       </c>
       <c r="I158" t="n">
-        <v>27.61</v>
+        <v>27.608</v>
       </c>
       <c r="J158" t="n">
-        <v>47.11</v>
+        <v>47.1132</v>
       </c>
       <c r="K158" t="n">
-        <v>46.84</v>
+        <v>46.8448</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>180068</v>
       </c>
       <c r="P158" t="n">
-        <v>95.03</v>
+        <v>95.0257</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -11556,13 +11556,13 @@
         <v>67167</v>
       </c>
       <c r="I159" t="n">
-        <v>28.13</v>
+        <v>28.129</v>
       </c>
       <c r="J159" t="n">
-        <v>44.3</v>
+        <v>44.2998</v>
       </c>
       <c r="K159" t="n">
-        <v>46.78</v>
+        <v>46.7762</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         <v>154702</v>
       </c>
       <c r="P159" t="n">
-        <v>90.14</v>
+        <v>90.1448</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -11624,13 +11624,13 @@
         <v>45174</v>
       </c>
       <c r="I160" t="n">
-        <v>21.98</v>
+        <v>21.9839</v>
       </c>
       <c r="J160" t="n">
-        <v>46.47</v>
+        <v>46.4716</v>
       </c>
       <c r="K160" t="n">
-        <v>49.4</v>
+        <v>49.4027</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>139413</v>
       </c>
       <c r="P160" t="n">
-        <v>86.95999999999999</v>
+        <v>86.96299999999999</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -11692,13 +11692,13 @@
         <v>44330</v>
       </c>
       <c r="I161" t="n">
-        <v>21.87</v>
+        <v>21.8659</v>
       </c>
       <c r="J161" t="n">
-        <v>50.24</v>
+        <v>50.2387</v>
       </c>
       <c r="K161" t="n">
-        <v>51.85</v>
+        <v>51.8522</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>138814</v>
       </c>
       <c r="P161" t="n">
-        <v>87.63</v>
+        <v>87.6318</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -11760,13 +11760,13 @@
         <v>64208</v>
       </c>
       <c r="I162" t="n">
-        <v>25.37</v>
+        <v>25.3739</v>
       </c>
       <c r="J162" t="n">
-        <v>46.51</v>
+        <v>46.5072</v>
       </c>
       <c r="K162" t="n">
-        <v>49.05</v>
+        <v>49.0508</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>167384</v>
       </c>
       <c r="P162" t="n">
-        <v>88.64</v>
+        <v>88.63849999999999</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -11828,13 +11828,13 @@
         <v>83323</v>
       </c>
       <c r="I163" t="n">
-        <v>39.74</v>
+        <v>39.7397</v>
       </c>
       <c r="J163" t="n">
-        <v>40.34</v>
+        <v>40.3421</v>
       </c>
       <c r="K163" t="n">
-        <v>46.69</v>
+        <v>46.6874</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>110122</v>
       </c>
       <c r="P163" t="n">
-        <v>87.16</v>
+        <v>87.157</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -11896,13 +11896,13 @@
         <v>57203</v>
       </c>
       <c r="I164" t="n">
-        <v>24.23</v>
+        <v>24.2303</v>
       </c>
       <c r="J164" t="n">
-        <v>47.21</v>
+        <v>47.2065</v>
       </c>
       <c r="K164" t="n">
-        <v>48.7</v>
+        <v>48.6977</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>165207</v>
       </c>
       <c r="P164" t="n">
-        <v>92.36</v>
+        <v>92.3579</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -11964,13 +11964,13 @@
         <v>63159</v>
       </c>
       <c r="I165" t="n">
-        <v>24.89</v>
+        <v>24.8895</v>
       </c>
       <c r="J165" t="n">
-        <v>47.52</v>
+        <v>47.5224</v>
       </c>
       <c r="K165" t="n">
-        <v>49.09</v>
+        <v>49.0853</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>174108</v>
       </c>
       <c r="P165" t="n">
-        <v>91.34999999999999</v>
+        <v>91.34780000000001</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -12032,13 +12032,13 @@
         <v>74681</v>
       </c>
       <c r="I166" t="n">
-        <v>37.84</v>
+        <v>37.8386</v>
       </c>
       <c r="J166" t="n">
-        <v>41.71</v>
+        <v>41.7096</v>
       </c>
       <c r="K166" t="n">
-        <v>46.49</v>
+        <v>46.4862</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>106847</v>
       </c>
       <c r="P166" t="n">
-        <v>87.09</v>
+        <v>87.0898</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -12100,13 +12100,13 @@
         <v>44785</v>
       </c>
       <c r="I167" t="n">
-        <v>25.36</v>
+        <v>25.359</v>
       </c>
       <c r="J167" t="n">
-        <v>47.06</v>
+        <v>47.0567</v>
       </c>
       <c r="K167" t="n">
-        <v>49.59</v>
+        <v>49.5854</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>116768</v>
       </c>
       <c r="P167" t="n">
-        <v>88.58</v>
+        <v>88.5821</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -12168,13 +12168,13 @@
         <v>44504</v>
       </c>
       <c r="I168" t="n">
-        <v>21.15</v>
+        <v>21.1511</v>
       </c>
       <c r="J168" t="n">
-        <v>48.48</v>
+        <v>48.4773</v>
       </c>
       <c r="K168" t="n">
-        <v>49.95</v>
+        <v>49.9536</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>150722</v>
       </c>
       <c r="P168" t="n">
-        <v>90.84999999999999</v>
+        <v>90.84780000000001</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -12236,13 +12236,13 @@
         <v>53529</v>
       </c>
       <c r="I169" t="n">
-        <v>24.17</v>
+        <v>24.1704</v>
       </c>
       <c r="J169" t="n">
-        <v>47.85</v>
+        <v>47.8459</v>
       </c>
       <c r="K169" t="n">
-        <v>48.96</v>
+        <v>48.9585</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>150542</v>
       </c>
       <c r="P169" t="n">
-        <v>89.64</v>
+        <v>89.6425</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
@@ -12304,13 +12304,13 @@
         <v>42381</v>
       </c>
       <c r="I170" t="n">
-        <v>24.09</v>
+        <v>24.0864</v>
       </c>
       <c r="J170" t="n">
-        <v>47.2</v>
+        <v>47.197</v>
       </c>
       <c r="K170" t="n">
-        <v>48.47</v>
+        <v>48.4701</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>117838</v>
       </c>
       <c r="P170" t="n">
-        <v>88.22</v>
+        <v>88.2199</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
@@ -12372,13 +12372,13 @@
         <v>74761</v>
       </c>
       <c r="I171" t="n">
-        <v>33.27</v>
+        <v>33.2701</v>
       </c>
       <c r="J171" t="n">
-        <v>45.69</v>
+        <v>45.6889</v>
       </c>
       <c r="K171" t="n">
-        <v>47.37</v>
+        <v>47.3691</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>133063</v>
       </c>
       <c r="P171" t="n">
-        <v>88.73999999999999</v>
+        <v>88.7394</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
@@ -12440,13 +12440,13 @@
         <v>54183</v>
       </c>
       <c r="I172" t="n">
-        <v>20.14</v>
+        <v>20.1421</v>
       </c>
       <c r="J172" t="n">
-        <v>48.26</v>
+        <v>48.2606</v>
       </c>
       <c r="K172" t="n">
-        <v>49.21</v>
+        <v>49.207</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>193459</v>
       </c>
       <c r="P172" t="n">
-        <v>90.06</v>
+        <v>90.05589999999999</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -12508,13 +12508,13 @@
         <v>43009</v>
       </c>
       <c r="I173" t="n">
-        <v>18.07</v>
+        <v>18.0731</v>
       </c>
       <c r="J173" t="n">
-        <v>50.06</v>
+        <v>50.0647</v>
       </c>
       <c r="K173" t="n">
-        <v>50.66</v>
+        <v>50.6588</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>181323</v>
       </c>
       <c r="P173" t="n">
-        <v>93</v>
+        <v>93.0038</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
@@ -12576,13 +12576,13 @@
         <v>61767</v>
       </c>
       <c r="I174" t="n">
-        <v>20.43</v>
+        <v>20.4274</v>
       </c>
       <c r="J174" t="n">
-        <v>49.22</v>
+        <v>49.2175</v>
       </c>
       <c r="K174" t="n">
-        <v>49.61</v>
+        <v>49.6141</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>222054</v>
       </c>
       <c r="P174" t="n">
-        <v>92.29000000000001</v>
+        <v>92.2891</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
@@ -12644,13 +12644,13 @@
         <v>44878</v>
       </c>
       <c r="I175" t="n">
-        <v>15.74</v>
+        <v>15.7395</v>
       </c>
       <c r="J175" t="n">
-        <v>49.28</v>
+        <v>49.2793</v>
       </c>
       <c r="K175" t="n">
-        <v>48.59</v>
+        <v>48.5915</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>229210</v>
       </c>
       <c r="P175" t="n">
-        <v>95.40000000000001</v>
+        <v>95.404</v>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
@@ -12712,13 +12712,13 @@
         <v>25544</v>
       </c>
       <c r="I176" t="n">
-        <v>9.32</v>
+        <v>9.321199999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>49.12</v>
+        <v>49.1182</v>
       </c>
       <c r="K176" t="n">
-        <v>47.67</v>
+        <v>47.6686</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>235163</v>
       </c>
       <c r="P176" t="n">
-        <v>94.63</v>
+        <v>94.6341</v>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
@@ -12780,13 +12780,13 @@
         <v>23076</v>
       </c>
       <c r="I177" t="n">
-        <v>9.550000000000001</v>
+        <v>9.553000000000001</v>
       </c>
       <c r="J177" t="n">
-        <v>49.29</v>
+        <v>49.2869</v>
       </c>
       <c r="K177" t="n">
-        <v>48.89</v>
+        <v>48.8908</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>208025</v>
       </c>
       <c r="P177" t="n">
-        <v>95.20999999999999</v>
+        <v>95.21420000000001</v>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
@@ -12848,13 +12848,13 @@
         <v>18691</v>
       </c>
       <c r="I178" t="n">
-        <v>8.01</v>
+        <v>8.009399999999999</v>
       </c>
       <c r="J178" t="n">
-        <v>48.92</v>
+        <v>48.9163</v>
       </c>
       <c r="K178" t="n">
-        <v>47.75</v>
+        <v>47.7526</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>203466</v>
       </c>
       <c r="P178" t="n">
-        <v>94.78</v>
+        <v>94.7804</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -12916,13 +12916,13 @@
         <v>11409</v>
       </c>
       <c r="I179" t="n">
-        <v>4.59</v>
+        <v>4.5918</v>
       </c>
       <c r="J179" t="n">
-        <v>49.1</v>
+        <v>49.1041</v>
       </c>
       <c r="K179" t="n">
-        <v>48.31</v>
+        <v>48.3133</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -12984,13 +12984,13 @@
         <v>6991</v>
       </c>
       <c r="I180" t="n">
-        <v>2.63</v>
+        <v>2.6255</v>
       </c>
       <c r="J180" t="n">
-        <v>49.15</v>
+        <v>49.148</v>
       </c>
       <c r="K180" t="n">
-        <v>48.95</v>
+        <v>48.9509</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>244669</v>
       </c>
       <c r="P180" t="n">
-        <v>94.37</v>
+        <v>94.3655</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -13055,10 +13055,10 @@
         <v>3.8</v>
       </c>
       <c r="J181" t="n">
-        <v>49.44</v>
+        <v>49.4388</v>
       </c>
       <c r="K181" t="n">
-        <v>48.87</v>
+        <v>48.865</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>218406</v>
       </c>
       <c r="P181" t="n">
-        <v>94.72</v>
+        <v>94.72110000000001</v>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
@@ -13120,13 +13120,13 @@
         <v>13096</v>
       </c>
       <c r="I182" t="n">
-        <v>4.85</v>
+        <v>4.849</v>
       </c>
       <c r="J182" t="n">
-        <v>48.91</v>
+        <v>48.9081</v>
       </c>
       <c r="K182" t="n">
-        <v>48.31</v>
+        <v>48.3069</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>237001</v>
       </c>
       <c r="P182" t="n">
-        <v>92.22</v>
+        <v>92.2247</v>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
@@ -13188,13 +13188,13 @@
         <v>12929</v>
       </c>
       <c r="I183" t="n">
-        <v>5.34</v>
+        <v>5.3421</v>
       </c>
       <c r="J183" t="n">
-        <v>49.31</v>
+        <v>49.3112</v>
       </c>
       <c r="K183" t="n">
-        <v>48.81</v>
+        <v>48.8081</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>213603</v>
       </c>
       <c r="P183" t="n">
-        <v>93.23999999999999</v>
+        <v>93.2394</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -13256,13 +13256,13 @@
         <v>27241</v>
       </c>
       <c r="I184" t="n">
-        <v>9.140000000000001</v>
+        <v>9.139799999999999</v>
       </c>
       <c r="J184" t="n">
-        <v>49.45</v>
+        <v>49.4526</v>
       </c>
       <c r="K184" t="n">
-        <v>48.57</v>
+        <v>48.5713</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>252515</v>
       </c>
       <c r="P184" t="n">
-        <v>93.25</v>
+        <v>93.2457</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -13324,13 +13324,13 @@
         <v>41481</v>
       </c>
       <c r="I185" t="n">
-        <v>13.35</v>
+        <v>13.3501</v>
       </c>
       <c r="J185" t="n">
-        <v>49.61</v>
+        <v>49.6078</v>
       </c>
       <c r="K185" t="n">
-        <v>49.4</v>
+        <v>49.4002</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>254187</v>
       </c>
       <c r="P185" t="n">
-        <v>94.41</v>
+        <v>94.4105</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -13392,13 +13392,13 @@
         <v>33188</v>
       </c>
       <c r="I186" t="n">
-        <v>12.69</v>
+        <v>12.6933</v>
       </c>
       <c r="J186" t="n">
-        <v>50.53</v>
+        <v>50.5293</v>
       </c>
       <c r="K186" t="n">
-        <v>50.59</v>
+        <v>50.5857</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>205454</v>
       </c>
       <c r="P186" t="n">
-        <v>90</v>
+        <v>90.004</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -13460,13 +13460,13 @@
         <v>49344</v>
       </c>
       <c r="I187" t="n">
-        <v>19.35</v>
+        <v>19.3501</v>
       </c>
       <c r="J187" t="n">
-        <v>48.56</v>
+        <v>48.5589</v>
       </c>
       <c r="K187" t="n">
-        <v>49.34</v>
+        <v>49.3392</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>186297</v>
       </c>
       <c r="P187" t="n">
-        <v>90.58</v>
+        <v>90.58410000000001</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -13528,13 +13528,13 @@
         <v>41546</v>
       </c>
       <c r="I188" t="n">
-        <v>15.77</v>
+        <v>15.7671</v>
       </c>
       <c r="J188" t="n">
-        <v>49.49</v>
+        <v>49.485</v>
       </c>
       <c r="K188" t="n">
-        <v>50.03</v>
+        <v>50.0252</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>204415</v>
       </c>
       <c r="P188" t="n">
-        <v>92.09999999999999</v>
+        <v>92.09869999999999</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -13596,13 +13596,13 @@
         <v>14059</v>
       </c>
       <c r="I189" t="n">
-        <v>5.59</v>
+        <v>5.5912</v>
       </c>
       <c r="J189" t="n">
-        <v>49.89</v>
+        <v>49.8861</v>
       </c>
       <c r="K189" t="n">
-        <v>49.75</v>
+        <v>49.7468</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>222573</v>
       </c>
       <c r="P189" t="n">
-        <v>93.76000000000001</v>
+        <v>93.75920000000001</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
@@ -13667,10 +13667,10 @@
         <v>13.31</v>
       </c>
       <c r="J190" t="n">
-        <v>50.35</v>
+        <v>50.352</v>
       </c>
       <c r="K190" t="n">
-        <v>50.76</v>
+        <v>50.7552</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>186909</v>
       </c>
       <c r="P190" t="n">
-        <v>91.87</v>
+        <v>91.8693</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -13732,13 +13732,13 @@
         <v>42072</v>
       </c>
       <c r="I191" t="n">
-        <v>13.24</v>
+        <v>13.2391</v>
       </c>
       <c r="J191" t="n">
-        <v>50.9</v>
+        <v>50.8982</v>
       </c>
       <c r="K191" t="n">
-        <v>50.62</v>
+        <v>50.6211</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>255204</v>
       </c>
       <c r="P191" t="n">
-        <v>92.56</v>
+        <v>92.5608</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -13800,13 +13800,13 @@
         <v>22549</v>
       </c>
       <c r="I192" t="n">
-        <v>8.59</v>
+        <v>8.585599999999999</v>
       </c>
       <c r="J192" t="n">
-        <v>49.64</v>
+        <v>49.6415</v>
       </c>
       <c r="K192" t="n">
-        <v>49.14</v>
+        <v>49.1445</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>226031</v>
       </c>
       <c r="P192" t="n">
-        <v>94.15000000000001</v>
+        <v>94.1451</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -13868,13 +13868,13 @@
         <v>26892</v>
       </c>
       <c r="I193" t="n">
-        <v>9.74</v>
+        <v>9.744400000000001</v>
       </c>
       <c r="J193" t="n">
-        <v>50.34</v>
+        <v>50.3415</v>
       </c>
       <c r="K193" t="n">
-        <v>49.92</v>
+        <v>49.9215</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>233718</v>
       </c>
       <c r="P193" t="n">
-        <v>93.83</v>
+        <v>93.8321</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -13936,13 +13936,13 @@
         <v>27541</v>
       </c>
       <c r="I194" t="n">
-        <v>11.58</v>
+        <v>11.5762</v>
       </c>
       <c r="J194" t="n">
-        <v>49.59</v>
+        <v>49.5862</v>
       </c>
       <c r="K194" t="n">
-        <v>49.38</v>
+        <v>49.3801</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>196584</v>
       </c>
       <c r="P194" t="n">
-        <v>93.45</v>
+        <v>93.4468</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -14004,13 +14004,13 @@
         <v>25862</v>
       </c>
       <c r="I195" t="n">
-        <v>9.49</v>
+        <v>9.494</v>
       </c>
       <c r="J195" t="n">
-        <v>49.55</v>
+        <v>49.5549</v>
       </c>
       <c r="K195" t="n">
-        <v>49.28</v>
+        <v>49.2839</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>227472</v>
       </c>
       <c r="P195" t="n">
-        <v>92.26000000000001</v>
+        <v>92.2646</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -14072,13 +14072,13 @@
         <v>14443</v>
       </c>
       <c r="I196" t="n">
-        <v>5.44</v>
+        <v>5.4397</v>
       </c>
       <c r="J196" t="n">
-        <v>49.34</v>
+        <v>49.3383</v>
       </c>
       <c r="K196" t="n">
-        <v>48.97</v>
+        <v>48.9674</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>232291</v>
       </c>
       <c r="P196" t="n">
-        <v>92.52</v>
+        <v>92.52079999999999</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -14140,13 +14140,13 @@
         <v>10042</v>
       </c>
       <c r="I197" t="n">
-        <v>3.66</v>
+        <v>3.6621</v>
       </c>
       <c r="J197" t="n">
-        <v>49.72</v>
+        <v>49.7234</v>
       </c>
       <c r="K197" t="n">
-        <v>49.53</v>
+        <v>49.5327</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>245994</v>
       </c>
       <c r="P197" t="n">
-        <v>93.12</v>
+        <v>93.1178</v>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
@@ -14208,13 +14208,13 @@
         <v>14935</v>
       </c>
       <c r="I198" t="n">
-        <v>5.38</v>
+        <v>5.3796</v>
       </c>
       <c r="J198" t="n">
-        <v>50.48</v>
+        <v>50.4827</v>
       </c>
       <c r="K198" t="n">
-        <v>49.95</v>
+        <v>49.9545</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>247691</v>
       </c>
       <c r="P198" t="n">
-        <v>94.29000000000001</v>
+        <v>94.2906</v>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
@@ -14276,13 +14276,13 @@
         <v>8806</v>
       </c>
       <c r="I199" t="n">
-        <v>3.61</v>
+        <v>3.6054</v>
       </c>
       <c r="J199" t="n">
-        <v>50.12</v>
+        <v>50.1234</v>
       </c>
       <c r="K199" t="n">
-        <v>49.85</v>
+        <v>49.8482</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>221578</v>
       </c>
       <c r="P199" t="n">
-        <v>94.11</v>
+        <v>94.11190000000001</v>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
@@ -14344,13 +14344,13 @@
         <v>8728</v>
       </c>
       <c r="I200" t="n">
-        <v>3.25</v>
+        <v>3.2529</v>
       </c>
       <c r="J200" t="n">
-        <v>49.25</v>
+        <v>49.2453</v>
       </c>
       <c r="K200" t="n">
-        <v>49</v>
+        <v>48.9988</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>240924</v>
       </c>
       <c r="P200" t="n">
-        <v>92.81</v>
+        <v>92.8094</v>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
@@ -14412,13 +14412,13 @@
         <v>12048</v>
       </c>
       <c r="I201" t="n">
-        <v>4.54</v>
+        <v>4.5411</v>
       </c>
       <c r="J201" t="n">
-        <v>49.55</v>
+        <v>49.5545</v>
       </c>
       <c r="K201" t="n">
-        <v>49.18</v>
+        <v>49.1819</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>235875</v>
       </c>
       <c r="P201" t="n">
-        <v>93.14</v>
+        <v>93.13549999999999</v>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
@@ -14480,13 +14480,13 @@
         <v>6344</v>
       </c>
       <c r="I202" t="n">
-        <v>2.49</v>
+        <v>2.4935</v>
       </c>
       <c r="J202" t="n">
-        <v>49.21</v>
+        <v>49.2135</v>
       </c>
       <c r="K202" t="n">
-        <v>48.93</v>
+        <v>48.9277</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>234321</v>
       </c>
       <c r="P202" t="n">
-        <v>94.45999999999999</v>
+        <v>94.45529999999999</v>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
@@ -14548,13 +14548,13 @@
         <v>18358</v>
       </c>
       <c r="I203" t="n">
-        <v>6.4</v>
+        <v>6.3981</v>
       </c>
       <c r="J203" t="n">
-        <v>48.76</v>
+        <v>48.7631</v>
       </c>
       <c r="K203" t="n">
-        <v>48.44</v>
+        <v>48.441</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>237135</v>
       </c>
       <c r="P203" t="n">
-        <v>88.3</v>
+        <v>88.2954</v>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
@@ -14616,13 +14616,13 @@
         <v>3684</v>
       </c>
       <c r="I204" t="n">
-        <v>1.32</v>
+        <v>1.3243</v>
       </c>
       <c r="J204" t="n">
-        <v>49.23</v>
+        <v>49.2279</v>
       </c>
       <c r="K204" t="n">
-        <v>49.04</v>
+        <v>49.0397</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>256930</v>
       </c>
       <c r="P204" t="n">
-        <v>93.59999999999999</v>
+        <v>93.59650000000001</v>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
@@ -14684,13 +14684,13 @@
         <v>6169</v>
       </c>
       <c r="I205" t="n">
-        <v>2.52</v>
+        <v>2.5212</v>
       </c>
       <c r="J205" t="n">
-        <v>48.89</v>
+        <v>48.888</v>
       </c>
       <c r="K205" t="n">
-        <v>48.55</v>
+        <v>48.5542</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>220737</v>
       </c>
       <c r="P205" t="n">
-        <v>92.54000000000001</v>
+        <v>92.5448</v>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
@@ -14752,13 +14752,13 @@
         <v>7308</v>
       </c>
       <c r="I206" t="n">
-        <v>2.55</v>
+        <v>2.5548</v>
       </c>
       <c r="J206" t="n">
-        <v>48.98</v>
+        <v>48.9778</v>
       </c>
       <c r="K206" t="n">
-        <v>48.63</v>
+        <v>48.6292</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>258432</v>
       </c>
       <c r="P206" t="n">
-        <v>92.70999999999999</v>
+        <v>92.71299999999999</v>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
@@ -14820,13 +14820,13 @@
         <v>2548</v>
       </c>
       <c r="I207" t="n">
-        <v>0.95</v>
+        <v>0.9525</v>
       </c>
       <c r="J207" t="n">
-        <v>48.39</v>
+        <v>48.3857</v>
       </c>
       <c r="K207" t="n">
-        <v>48.18</v>
+        <v>48.1815</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>246333</v>
       </c>
       <c r="P207" t="n">
-        <v>92.97</v>
+        <v>92.96599999999999</v>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
@@ -14888,13 +14888,13 @@
         <v>2581</v>
       </c>
       <c r="I208" t="n">
-        <v>0.97</v>
+        <v>0.9666</v>
       </c>
       <c r="J208" t="n">
-        <v>48.75</v>
+        <v>48.7521</v>
       </c>
       <c r="K208" t="n">
-        <v>48.53</v>
+        <v>48.5303</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>249316</v>
       </c>
       <c r="P208" t="n">
-        <v>94.28</v>
+        <v>94.2818</v>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
@@ -14956,13 +14956,13 @@
         <v>2730</v>
       </c>
       <c r="I209" t="n">
-        <v>1.07</v>
+        <v>1.0654</v>
       </c>
       <c r="J209" t="n">
-        <v>49.09</v>
+        <v>49.0878</v>
       </c>
       <c r="K209" t="n">
-        <v>48.77</v>
+        <v>48.7699</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>238188</v>
       </c>
       <c r="P209" t="n">
-        <v>93.95</v>
+        <v>93.9512</v>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
@@ -15024,13 +15024,13 @@
         <v>11362</v>
       </c>
       <c r="I210" t="n">
-        <v>4.32</v>
+        <v>4.3155</v>
       </c>
       <c r="J210" t="n">
-        <v>48.85</v>
+        <v>48.8508</v>
       </c>
       <c r="K210" t="n">
-        <v>48.62</v>
+        <v>48.6216</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>239446</v>
       </c>
       <c r="P210" t="n">
-        <v>95.05</v>
+        <v>95.0488</v>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
@@ -15092,13 +15092,13 @@
         <v>7375</v>
       </c>
       <c r="I211" t="n">
-        <v>2.69</v>
+        <v>2.6937</v>
       </c>
       <c r="J211" t="n">
-        <v>48.34</v>
+        <v>48.3447</v>
       </c>
       <c r="K211" t="n">
-        <v>47.85</v>
+        <v>47.8502</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>252722</v>
       </c>
       <c r="P211" t="n">
-        <v>94.86</v>
+        <v>94.8603</v>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
@@ -15160,13 +15160,13 @@
         <v>2601</v>
       </c>
       <c r="I212" t="n">
-        <v>1.01</v>
+        <v>1.0061</v>
       </c>
       <c r="J212" t="n">
-        <v>48.47</v>
+        <v>48.4723</v>
       </c>
       <c r="K212" t="n">
-        <v>48.16</v>
+        <v>48.1647</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>241957</v>
       </c>
       <c r="P212" t="n">
-        <v>94.54000000000001</v>
+        <v>94.5425</v>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
@@ -15228,13 +15228,13 @@
         <v>839</v>
       </c>
       <c r="I213" t="n">
-        <v>0.34</v>
+        <v>0.3385</v>
       </c>
       <c r="J213" t="n">
-        <v>48.39</v>
+        <v>48.3923</v>
       </c>
       <c r="K213" t="n">
-        <v>48.05</v>
+        <v>48.0527</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>232048</v>
       </c>
       <c r="P213" t="n">
-        <v>93.93000000000001</v>
+        <v>93.9325</v>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
@@ -15296,13 +15296,13 @@
         <v>3008</v>
       </c>
       <c r="I214" t="n">
-        <v>1.13</v>
+        <v>1.1282</v>
       </c>
       <c r="J214" t="n">
-        <v>48.48</v>
+        <v>48.4768</v>
       </c>
       <c r="K214" t="n">
-        <v>48.19</v>
+        <v>48.1897</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>249421</v>
       </c>
       <c r="P214" t="n">
-        <v>94.62</v>
+        <v>94.6203</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -15364,13 +15364,13 @@
         <v>1097</v>
       </c>
       <c r="I215" t="n">
-        <v>0.41</v>
+        <v>0.4142</v>
       </c>
       <c r="J215" t="n">
-        <v>48.28</v>
+        <v>48.2792</v>
       </c>
       <c r="K215" t="n">
-        <v>48.03</v>
+        <v>48.0334</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>247653</v>
       </c>
       <c r="P215" t="n">
-        <v>93.89</v>
+        <v>93.88800000000001</v>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
@@ -15432,13 +15432,13 @@
         <v>1944</v>
       </c>
       <c r="I216" t="n">
-        <v>0.78</v>
+        <v>0.7778</v>
       </c>
       <c r="J216" t="n">
-        <v>48.19</v>
+        <v>48.1882</v>
       </c>
       <c r="K216" t="n">
-        <v>47.78</v>
+        <v>47.7772</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>236328</v>
       </c>
       <c r="P216" t="n">
-        <v>95.3</v>
+        <v>95.3028</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -15500,13 +15500,13 @@
         <v>4867</v>
       </c>
       <c r="I217" t="n">
-        <v>2.09</v>
+        <v>2.0904</v>
       </c>
       <c r="J217" t="n">
-        <v>49.52</v>
+        <v>49.5179</v>
       </c>
       <c r="K217" t="n">
-        <v>49.18</v>
+        <v>49.1823</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>212835</v>
       </c>
       <c r="P217" t="n">
-        <v>93.37</v>
+        <v>93.36750000000001</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
@@ -15568,13 +15568,13 @@
         <v>4661</v>
       </c>
       <c r="I218" t="n">
-        <v>1.7</v>
+        <v>1.7016</v>
       </c>
       <c r="J218" t="n">
-        <v>49.17</v>
+        <v>49.1704</v>
       </c>
       <c r="K218" t="n">
-        <v>48.91</v>
+        <v>48.9096</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>244842</v>
       </c>
       <c r="P218" t="n">
-        <v>90.93000000000001</v>
+        <v>90.9341</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -15636,13 +15636,13 @@
         <v>6591</v>
       </c>
       <c r="I219" t="n">
-        <v>2.21</v>
+        <v>2.2103</v>
       </c>
       <c r="J219" t="n">
-        <v>48.95</v>
+        <v>48.9542</v>
       </c>
       <c r="K219" t="n">
-        <v>48.47</v>
+        <v>48.4657</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>269373</v>
       </c>
       <c r="P219" t="n">
-        <v>92.38</v>
+        <v>92.37820000000001</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -15704,13 +15704,13 @@
         <v>6779</v>
       </c>
       <c r="I220" t="n">
-        <v>2.79</v>
+        <v>2.7903</v>
       </c>
       <c r="J220" t="n">
-        <v>48.9</v>
+        <v>48.895</v>
       </c>
       <c r="K220" t="n">
-        <v>48.18</v>
+        <v>48.1801</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>218374</v>
       </c>
       <c r="P220" t="n">
-        <v>92.47</v>
+        <v>92.46550000000001</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -15772,13 +15772,13 @@
         <v>19065</v>
       </c>
       <c r="I221" t="n">
-        <v>7.75</v>
+        <v>7.7513</v>
       </c>
       <c r="J221" t="n">
-        <v>50.71</v>
+        <v>50.7145</v>
       </c>
       <c r="K221" t="n">
-        <v>48.66</v>
+        <v>48.661</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>207713</v>
       </c>
       <c r="P221" t="n">
-        <v>91.55</v>
+        <v>91.5463</v>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
@@ -15840,13 +15840,13 @@
         <v>7660</v>
       </c>
       <c r="I222" t="n">
-        <v>3.25</v>
+        <v>3.2533</v>
       </c>
       <c r="J222" t="n">
-        <v>50.07</v>
+        <v>50.0699</v>
       </c>
       <c r="K222" t="n">
-        <v>49.5</v>
+        <v>49.5024</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>213383</v>
       </c>
       <c r="P222" t="n">
-        <v>93.67</v>
+        <v>93.6741</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -15908,13 +15908,13 @@
         <v>7449</v>
       </c>
       <c r="I223" t="n">
-        <v>3.07</v>
+        <v>3.0705</v>
       </c>
       <c r="J223" t="n">
-        <v>49.26</v>
+        <v>49.2589</v>
       </c>
       <c r="K223" t="n">
-        <v>50.31</v>
+        <v>50.3064</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>220940</v>
       </c>
       <c r="P223" t="n">
-        <v>93.95999999999999</v>
+        <v>93.95820000000001</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -15976,13 +15976,13 @@
         <v>9853</v>
       </c>
       <c r="I224" t="n">
-        <v>3.96</v>
+        <v>3.963</v>
       </c>
       <c r="J224" t="n">
-        <v>49.52</v>
+        <v>49.5198</v>
       </c>
       <c r="K224" t="n">
-        <v>48.72</v>
+        <v>48.7224</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>223842</v>
       </c>
       <c r="P224" t="n">
-        <v>93.75</v>
+        <v>93.7484</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -16044,13 +16044,13 @@
         <v>58938</v>
       </c>
       <c r="I225" t="n">
-        <v>24.61</v>
+        <v>24.6121</v>
       </c>
       <c r="J225" t="n">
-        <v>51.25</v>
+        <v>51.249</v>
       </c>
       <c r="K225" t="n">
-        <v>50.71</v>
+        <v>50.7074</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>161661</v>
       </c>
       <c r="P225" t="n">
-        <v>89.55</v>
+        <v>89.548</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -16112,13 +16112,13 @@
         <v>13369</v>
       </c>
       <c r="I226" t="n">
-        <v>5.3</v>
+        <v>5.2961</v>
       </c>
       <c r="J226" t="n">
-        <v>49.6</v>
+        <v>49.5969</v>
       </c>
       <c r="K226" t="n">
-        <v>48.78</v>
+        <v>48.784</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>225543</v>
       </c>
       <c r="P226" t="n">
-        <v>94.34</v>
+        <v>94.3442</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -16180,13 +16180,13 @@
         <v>1989</v>
       </c>
       <c r="I227" t="n">
-        <v>0.72</v>
+        <v>0.7197</v>
       </c>
       <c r="J227" t="n">
         <v>48.68</v>
       </c>
       <c r="K227" t="n">
-        <v>48.31</v>
+        <v>48.308</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>257340</v>
       </c>
       <c r="P227" t="n">
-        <v>93.79000000000001</v>
+        <v>93.7886</v>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
@@ -16248,13 +16248,13 @@
         <v>8991</v>
       </c>
       <c r="I228" t="n">
-        <v>3.39</v>
+        <v>3.3943</v>
       </c>
       <c r="J228" t="n">
-        <v>49.5</v>
+        <v>49.5015</v>
       </c>
       <c r="K228" t="n">
-        <v>48.96</v>
+        <v>48.9609</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>242754</v>
       </c>
       <c r="P228" t="n">
-        <v>94.87</v>
+        <v>94.86579999999999</v>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
@@ -16316,13 +16316,13 @@
         <v>20318</v>
       </c>
       <c r="I229" t="n">
-        <v>8.52</v>
+        <v>8.5205</v>
       </c>
       <c r="J229" t="n">
-        <v>50.01</v>
+        <v>50.0055</v>
       </c>
       <c r="K229" t="n">
-        <v>49.66</v>
+        <v>49.6594</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>208560</v>
       </c>
       <c r="P229" t="n">
-        <v>95.61</v>
+        <v>95.6074</v>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
@@ -16384,13 +16384,13 @@
         <v>7611</v>
       </c>
       <c r="I230" t="n">
-        <v>3.18</v>
+        <v>3.1778</v>
       </c>
       <c r="J230" t="n">
-        <v>50.01</v>
+        <v>50.0073</v>
       </c>
       <c r="K230" t="n">
-        <v>49.78</v>
+        <v>49.784</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
         <v>217323</v>
       </c>
       <c r="P230" t="n">
-        <v>93.70999999999999</v>
+        <v>93.7149</v>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
@@ -16452,13 +16452,13 @@
         <v>11983</v>
       </c>
       <c r="I231" t="n">
-        <v>3.89</v>
+        <v>3.8902</v>
       </c>
       <c r="J231" t="n">
-        <v>49.52</v>
+        <v>49.5153</v>
       </c>
       <c r="K231" t="n">
-        <v>49.36</v>
+        <v>49.3648</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>252047</v>
       </c>
       <c r="P231" t="n">
-        <v>85.14</v>
+        <v>85.13809999999999</v>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
@@ -16520,13 +16520,13 @@
         <v>11748</v>
       </c>
       <c r="I232" t="n">
-        <v>4.07</v>
+        <v>4.0747</v>
       </c>
       <c r="J232" t="n">
-        <v>49.19</v>
+        <v>49.1858</v>
       </c>
       <c r="K232" t="n">
-        <v>48.95</v>
+        <v>48.9498</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>242025</v>
       </c>
       <c r="P232" t="n">
-        <v>87.51000000000001</v>
+        <v>87.5098</v>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
@@ -16588,13 +16588,13 @@
         <v>7008</v>
       </c>
       <c r="I233" t="n">
-        <v>2.42</v>
+        <v>2.418</v>
       </c>
       <c r="J233" t="n">
-        <v>49.11</v>
+        <v>49.1133</v>
       </c>
       <c r="K233" t="n">
-        <v>48.73</v>
+        <v>48.7306</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>264690</v>
       </c>
       <c r="P233" t="n">
-        <v>93.59</v>
+        <v>93.5896</v>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
@@ -16656,13 +16656,13 @@
         <v>4253</v>
       </c>
       <c r="I234" t="n">
-        <v>1.79</v>
+        <v>1.7935</v>
       </c>
       <c r="J234" t="n">
-        <v>49.47</v>
+        <v>49.4678</v>
       </c>
       <c r="K234" t="n">
-        <v>48.62</v>
+        <v>48.6227</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>222049</v>
       </c>
       <c r="P234" t="n">
-        <v>95.34999999999999</v>
+        <v>95.34869999999999</v>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
@@ -16724,13 +16724,13 @@
         <v>9883</v>
       </c>
       <c r="I235" t="n">
-        <v>3.42</v>
+        <v>3.4175</v>
       </c>
       <c r="J235" t="n">
-        <v>49.89</v>
+        <v>49.8937</v>
       </c>
       <c r="K235" t="n">
-        <v>49.54</v>
+        <v>49.5371</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>266475</v>
       </c>
       <c r="P235" t="n">
-        <v>95.41</v>
+        <v>95.4068</v>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
@@ -16792,13 +16792,13 @@
         <v>8750</v>
       </c>
       <c r="I236" t="n">
-        <v>3.16</v>
+        <v>3.1613</v>
       </c>
       <c r="J236" t="n">
-        <v>48.71</v>
+        <v>48.7105</v>
       </c>
       <c r="K236" t="n">
-        <v>48.11</v>
+        <v>48.1088</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>253963</v>
       </c>
       <c r="P236" t="n">
-        <v>94.75</v>
+        <v>94.7503</v>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
@@ -16860,13 +16860,13 @@
         <v>30829</v>
       </c>
       <c r="I237" t="n">
-        <v>10.59</v>
+        <v>10.5896</v>
       </c>
       <c r="J237" t="n">
         <v>50.79</v>
       </c>
       <c r="K237" t="n">
-        <v>50.5</v>
+        <v>50.4992</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>244086</v>
       </c>
       <c r="P237" t="n">
-        <v>93.77</v>
+        <v>93.7728</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
@@ -16928,13 +16928,13 @@
         <v>10636</v>
       </c>
       <c r="I238" t="n">
-        <v>4.59</v>
+        <v>4.5892</v>
       </c>
       <c r="J238" t="n">
-        <v>50.7</v>
+        <v>50.7001</v>
       </c>
       <c r="K238" t="n">
-        <v>50.14</v>
+        <v>50.1404</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>208079</v>
       </c>
       <c r="P238" t="n">
-        <v>94.09999999999999</v>
+        <v>94.1002</v>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
@@ -16996,13 +16996,13 @@
         <v>11738</v>
       </c>
       <c r="I239" t="n">
-        <v>3.94</v>
+        <v>3.9428</v>
       </c>
       <c r="J239" t="n">
-        <v>49.88</v>
+        <v>49.8824</v>
       </c>
       <c r="K239" t="n">
-        <v>49.16</v>
+        <v>49.1621</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>266178</v>
       </c>
       <c r="P239" t="n">
-        <v>93.08</v>
+        <v>93.08029999999999</v>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
@@ -17064,13 +17064,13 @@
         <v>15292</v>
       </c>
       <c r="I240" t="n">
-        <v>6.1</v>
+        <v>6.1002</v>
       </c>
       <c r="J240" t="n">
-        <v>48.96</v>
+        <v>48.958</v>
       </c>
       <c r="K240" t="n">
-        <v>48.03</v>
+        <v>48.0326</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>219946</v>
       </c>
       <c r="P240" t="n">
-        <v>93.44</v>
+        <v>93.43980000000001</v>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
@@ -17132,13 +17132,13 @@
         <v>15768</v>
       </c>
       <c r="I241" t="n">
-        <v>5.92</v>
+        <v>5.9184</v>
       </c>
       <c r="J241" t="n">
-        <v>49.14</v>
+        <v>49.1384</v>
       </c>
       <c r="K241" t="n">
-        <v>48.24</v>
+        <v>48.2356</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>230137</v>
       </c>
       <c r="P241" t="n">
-        <v>91.81</v>
+        <v>91.8135</v>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
@@ -17200,13 +17200,13 @@
         <v>13223</v>
       </c>
       <c r="I242" t="n">
-        <v>4.95</v>
+        <v>4.9515</v>
       </c>
       <c r="J242" t="n">
-        <v>48.88</v>
+        <v>48.8785</v>
       </c>
       <c r="K242" t="n">
-        <v>47.94</v>
+        <v>47.9437</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>233203</v>
       </c>
       <c r="P242" t="n">
-        <v>91.88</v>
+        <v>91.8755</v>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
@@ -17268,13 +17268,13 @@
         <v>19287</v>
       </c>
       <c r="I243" t="n">
-        <v>7.11</v>
+        <v>7.1143</v>
       </c>
       <c r="J243" t="n">
-        <v>49.61</v>
+        <v>49.6073</v>
       </c>
       <c r="K243" t="n">
-        <v>48.93</v>
+        <v>48.9258</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>230653</v>
       </c>
       <c r="P243" t="n">
-        <v>91.59999999999999</v>
+        <v>91.5958</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -17336,13 +17336,13 @@
         <v>9900</v>
       </c>
       <c r="I244" t="n">
-        <v>3.73</v>
+        <v>3.7308</v>
       </c>
       <c r="J244" t="n">
-        <v>49.97</v>
+        <v>49.9744</v>
       </c>
       <c r="K244" t="n">
-        <v>49.32</v>
+        <v>49.3236</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>236467</v>
       </c>
       <c r="P244" t="n">
-        <v>92.56999999999999</v>
+        <v>92.5652</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -17404,13 +17404,13 @@
         <v>17261</v>
       </c>
       <c r="I245" t="n">
-        <v>6.99</v>
+        <v>6.9936</v>
       </c>
       <c r="J245" t="n">
-        <v>50.03</v>
+        <v>50.0278</v>
       </c>
       <c r="K245" t="n">
-        <v>49.23</v>
+        <v>49.2311</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>211974</v>
       </c>
       <c r="P245" t="n">
-        <v>92.34</v>
+        <v>92.3425</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -17472,13 +17472,13 @@
         <v>19571</v>
       </c>
       <c r="I246" t="n">
-        <v>7.65</v>
+        <v>7.6542</v>
       </c>
       <c r="J246" t="n">
-        <v>48.8</v>
+        <v>48.7987</v>
       </c>
       <c r="K246" t="n">
-        <v>47.89</v>
+        <v>47.8913</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>215946</v>
       </c>
       <c r="P246" t="n">
-        <v>91.45999999999999</v>
+        <v>91.456</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -17540,13 +17540,13 @@
         <v>18584</v>
       </c>
       <c r="I247" t="n">
-        <v>6.82</v>
+        <v>6.8171</v>
       </c>
       <c r="J247" t="n">
-        <v>49.62</v>
+        <v>49.6168</v>
       </c>
       <c r="K247" t="n">
-        <v>48.98</v>
+        <v>48.9759</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>234431</v>
       </c>
       <c r="P247" t="n">
-        <v>92.29000000000001</v>
+        <v>92.2873</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -17608,13 +17608,13 @@
         <v>9387</v>
       </c>
       <c r="I248" t="n">
-        <v>3.87</v>
+        <v>3.8699</v>
       </c>
       <c r="J248" t="n">
-        <v>48.97</v>
+        <v>48.9697</v>
       </c>
       <c r="K248" t="n">
-        <v>48.52</v>
+        <v>48.5164</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>218491</v>
       </c>
       <c r="P248" t="n">
-        <v>93.7</v>
+        <v>93.7026</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -17676,13 +17676,13 @@
         <v>10202</v>
       </c>
       <c r="I249" t="n">
-        <v>4.04</v>
+        <v>4.0427</v>
       </c>
       <c r="J249" t="n">
-        <v>49.17</v>
+        <v>49.1744</v>
       </c>
       <c r="K249" t="n">
-        <v>48.69</v>
+        <v>48.6948</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>221957</v>
       </c>
       <c r="P249" t="n">
-        <v>91.66</v>
+        <v>91.6606</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -17744,13 +17744,13 @@
         <v>8498</v>
       </c>
       <c r="I250" t="n">
-        <v>3.23</v>
+        <v>3.2303</v>
       </c>
       <c r="J250" t="n">
-        <v>49.84</v>
+        <v>49.835</v>
       </c>
       <c r="K250" t="n">
-        <v>49.45</v>
+        <v>49.4453</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>236828</v>
       </c>
       <c r="P250" t="n">
-        <v>93.03</v>
+        <v>93.03060000000001</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -17812,13 +17812,13 @@
         <v>6401</v>
       </c>
       <c r="I251" t="n">
-        <v>2.78</v>
+        <v>2.7768</v>
       </c>
       <c r="J251" t="n">
-        <v>50</v>
+        <v>50.0007</v>
       </c>
       <c r="K251" t="n">
-        <v>49.5</v>
+        <v>49.5043</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>210215</v>
       </c>
       <c r="P251" t="n">
-        <v>93.8</v>
+        <v>93.7957</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -17880,13 +17880,13 @@
         <v>5520</v>
       </c>
       <c r="I252" t="n">
-        <v>2.29</v>
+        <v>2.2885</v>
       </c>
       <c r="J252" t="n">
-        <v>49.27</v>
+        <v>49.2705</v>
       </c>
       <c r="K252" t="n">
-        <v>48.9</v>
+        <v>48.8953</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>219936</v>
       </c>
       <c r="P252" t="n">
-        <v>93.31999999999999</v>
+        <v>93.31780000000001</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -17948,13 +17948,13 @@
         <v>17378</v>
       </c>
       <c r="I253" t="n">
-        <v>6.25</v>
+        <v>6.2451</v>
       </c>
       <c r="J253" t="n">
-        <v>50.14</v>
+        <v>50.1376</v>
       </c>
       <c r="K253" t="n">
-        <v>49.9</v>
+        <v>49.8961</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>239331</v>
       </c>
       <c r="P253" t="n">
-        <v>91.73999999999999</v>
+        <v>91.73779999999999</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -18016,13 +18016,13 @@
         <v>9208</v>
       </c>
       <c r="I254" t="n">
-        <v>3.53</v>
+        <v>3.5332</v>
       </c>
       <c r="J254" t="n">
-        <v>49.41</v>
+        <v>49.4125</v>
       </c>
       <c r="K254" t="n">
-        <v>48.94</v>
+        <v>48.9395</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>235362</v>
       </c>
       <c r="P254" t="n">
-        <v>93.62</v>
+        <v>93.6198</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -18084,13 +18084,13 @@
         <v>7398</v>
       </c>
       <c r="I255" t="n">
-        <v>2.74</v>
+        <v>2.742</v>
       </c>
       <c r="J255" t="n">
-        <v>49.07</v>
+        <v>49.0741</v>
       </c>
       <c r="K255" t="n">
-        <v>48.78</v>
+        <v>48.7805</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>246292</v>
       </c>
       <c r="P255" t="n">
-        <v>93.86</v>
+        <v>93.8584</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
@@ -18152,13 +18152,13 @@
         <v>8424</v>
       </c>
       <c r="I256" t="n">
-        <v>3.68</v>
+        <v>3.6833</v>
       </c>
       <c r="J256" t="n">
-        <v>49.73</v>
+        <v>49.7259</v>
       </c>
       <c r="K256" t="n">
-        <v>49.37</v>
+        <v>49.3695</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>207478</v>
       </c>
       <c r="P256" t="n">
-        <v>94.19</v>
+        <v>94.1866</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -18220,13 +18220,13 @@
         <v>985</v>
       </c>
       <c r="I257" t="n">
-        <v>0.39</v>
+        <v>0.3868</v>
       </c>
       <c r="J257" t="n">
-        <v>49.13</v>
+        <v>49.1256</v>
       </c>
       <c r="K257" t="n">
-        <v>48.96</v>
+        <v>48.9564</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>240253</v>
       </c>
       <c r="P257" t="n">
-        <v>94.7</v>
+        <v>94.7008</v>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
@@ -18288,13 +18288,13 @@
         <v>4040</v>
       </c>
       <c r="I258" t="n">
-        <v>1.62</v>
+        <v>1.6205</v>
       </c>
       <c r="J258" t="n">
-        <v>49.31</v>
+        <v>49.3147</v>
       </c>
       <c r="K258" t="n">
-        <v>49.08</v>
+        <v>49.0763</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>232394</v>
       </c>
       <c r="P258" t="n">
-        <v>94.75</v>
+        <v>94.7514</v>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
@@ -18356,13 +18356,13 @@
         <v>5321</v>
       </c>
       <c r="I259" t="n">
-        <v>2.21</v>
+        <v>2.2071</v>
       </c>
       <c r="J259" t="n">
-        <v>49.19</v>
+        <v>49.1852</v>
       </c>
       <c r="K259" t="n">
-        <v>48.85</v>
+        <v>48.8544</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>221852</v>
       </c>
       <c r="P259" t="n">
-        <v>94.09999999999999</v>
+        <v>94.0968</v>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
@@ -18424,13 +18424,13 @@
         <v>16385</v>
       </c>
       <c r="I260" t="n">
-        <v>6.55</v>
+        <v>6.5523</v>
       </c>
       <c r="J260" t="n">
-        <v>49.52</v>
+        <v>49.5189</v>
       </c>
       <c r="K260" t="n">
-        <v>49.48</v>
+        <v>49.4824</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>223246</v>
       </c>
       <c r="P260" t="n">
-        <v>95.54000000000001</v>
+        <v>95.53530000000001</v>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
@@ -18492,13 +18492,13 @@
         <v>35967</v>
       </c>
       <c r="I261" t="n">
-        <v>13.94</v>
+        <v>13.9446</v>
       </c>
       <c r="J261" t="n">
-        <v>50.93</v>
+        <v>50.9309</v>
       </c>
       <c r="K261" t="n">
-        <v>51.05</v>
+        <v>51.0495</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>204823</v>
       </c>
       <c r="P261" t="n">
-        <v>92.28</v>
+        <v>92.2788</v>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
@@ -18560,13 +18560,13 @@
         <v>18639</v>
       </c>
       <c r="I262" t="n">
-        <v>7.04</v>
+        <v>7.0416</v>
       </c>
       <c r="J262" t="n">
-        <v>49.41</v>
+        <v>49.415</v>
       </c>
       <c r="K262" t="n">
-        <v>49.25</v>
+        <v>49.2506</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>233245</v>
       </c>
       <c r="P262" t="n">
-        <v>94.79000000000001</v>
+        <v>94.7919</v>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
@@ -18628,13 +18628,13 @@
         <v>16337</v>
       </c>
       <c r="I263" t="n">
-        <v>6.76</v>
+        <v>6.7563</v>
       </c>
       <c r="J263" t="n">
-        <v>49.71</v>
+        <v>49.7124</v>
       </c>
       <c r="K263" t="n">
-        <v>49.33</v>
+        <v>49.3254</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>214774</v>
       </c>
       <c r="P263" t="n">
-        <v>95.26000000000001</v>
+        <v>95.25700000000001</v>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
@@ -18696,13 +18696,13 @@
         <v>32093</v>
       </c>
       <c r="I264" t="n">
-        <v>12.9</v>
+        <v>12.8962</v>
       </c>
       <c r="J264" t="n">
-        <v>49.37</v>
+        <v>49.3741</v>
       </c>
       <c r="K264" t="n">
-        <v>49.35</v>
+        <v>49.3491</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>204165</v>
       </c>
       <c r="P264" t="n">
-        <v>94.19</v>
+        <v>94.18770000000001</v>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
@@ -18764,13 +18764,13 @@
         <v>20841</v>
       </c>
       <c r="I265" t="n">
-        <v>8.43</v>
+        <v>8.4305</v>
       </c>
       <c r="J265" t="n">
-        <v>49.35</v>
+        <v>49.3538</v>
       </c>
       <c r="K265" t="n">
-        <v>48.97</v>
+        <v>48.9703</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>213233</v>
       </c>
       <c r="P265" t="n">
-        <v>94.2</v>
+        <v>94.19670000000001</v>
       </c>
       <c r="Q265" t="inlineStr">
         <is>
@@ -18832,13 +18832,13 @@
         <v>17653</v>
       </c>
       <c r="I266" t="n">
-        <v>6.86</v>
+        <v>6.8621</v>
       </c>
       <c r="J266" t="n">
-        <v>50.14</v>
+        <v>50.1388</v>
       </c>
       <c r="K266" t="n">
-        <v>49.63</v>
+        <v>49.6263</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>227492</v>
       </c>
       <c r="P266" t="n">
-        <v>94.95</v>
+        <v>94.9462</v>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
@@ -18900,13 +18900,13 @@
         <v>24887</v>
       </c>
       <c r="I267" t="n">
-        <v>8.720000000000001</v>
+        <v>8.7247</v>
       </c>
       <c r="J267" t="n">
-        <v>50.32</v>
+        <v>50.3174</v>
       </c>
       <c r="K267" t="n">
-        <v>50.11</v>
+        <v>50.1106</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>247932</v>
       </c>
       <c r="P267" t="n">
-        <v>95.23</v>
+        <v>95.2266</v>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
@@ -18968,13 +18968,13 @@
         <v>28641</v>
       </c>
       <c r="I268" t="n">
-        <v>11.22</v>
+        <v>11.2193</v>
       </c>
       <c r="J268" t="n">
-        <v>49.91</v>
+        <v>49.9054</v>
       </c>
       <c r="K268" t="n">
-        <v>49.82</v>
+        <v>49.8173</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>214694</v>
       </c>
       <c r="P268" t="n">
-        <v>94.73</v>
+        <v>94.7282</v>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
@@ -19036,13 +19036,13 @@
         <v>21140</v>
       </c>
       <c r="I269" t="n">
-        <v>8.33</v>
+        <v>8.332100000000001</v>
       </c>
       <c r="J269" t="n">
-        <v>48.94</v>
+        <v>48.9439</v>
       </c>
       <c r="K269" t="n">
-        <v>48.28</v>
+        <v>48.2761</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>220056</v>
       </c>
       <c r="P269" t="n">
-        <v>94.62</v>
+        <v>94.6164</v>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
@@ -19104,13 +19104,13 @@
         <v>22015</v>
       </c>
       <c r="I270" t="n">
-        <v>8.42</v>
+        <v>8.418900000000001</v>
       </c>
       <c r="J270" t="n">
-        <v>48.32</v>
+        <v>48.321</v>
       </c>
       <c r="K270" t="n">
-        <v>47.45</v>
+        <v>47.4466</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>224880</v>
       </c>
       <c r="P270" t="n">
-        <v>93.90000000000001</v>
+        <v>93.90349999999999</v>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
@@ -19172,13 +19172,13 @@
         <v>18341</v>
       </c>
       <c r="I271" t="n">
-        <v>6.67</v>
+        <v>6.6658</v>
       </c>
       <c r="J271" t="n">
-        <v>49.2</v>
+        <v>49.2044</v>
       </c>
       <c r="K271" t="n">
-        <v>48.83</v>
+        <v>48.8277</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>239536</v>
       </c>
       <c r="P271" t="n">
-        <v>93.27</v>
+        <v>93.27330000000001</v>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
@@ -19240,13 +19240,13 @@
         <v>35111</v>
       </c>
       <c r="I272" t="n">
-        <v>13.05</v>
+        <v>13.0453</v>
       </c>
       <c r="J272" t="n">
-        <v>48.62</v>
+        <v>48.6152</v>
       </c>
       <c r="K272" t="n">
-        <v>48.47</v>
+        <v>48.4684</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>219183</v>
       </c>
       <c r="P272" t="n">
-        <v>93.65000000000001</v>
+        <v>93.65389999999999</v>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
@@ -19308,13 +19308,13 @@
         <v>27631</v>
       </c>
       <c r="I273" t="n">
-        <v>10.64</v>
+        <v>10.6431</v>
       </c>
       <c r="J273" t="n">
-        <v>48.88</v>
+        <v>48.8781</v>
       </c>
       <c r="K273" t="n">
-        <v>48.77</v>
+        <v>48.7684</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>219247</v>
       </c>
       <c r="P273" t="n">
-        <v>94.51000000000001</v>
+        <v>94.5095</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -19376,13 +19376,13 @@
         <v>16671</v>
       </c>
       <c r="I274" t="n">
-        <v>6.6</v>
+        <v>6.5976</v>
       </c>
       <c r="J274" t="n">
-        <v>49.72</v>
+        <v>49.7196</v>
       </c>
       <c r="K274" t="n">
-        <v>49.42</v>
+        <v>49.4233</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>225886</v>
       </c>
       <c r="P274" t="n">
-        <v>95.70999999999999</v>
+        <v>95.71040000000001</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -19444,13 +19444,13 @@
         <v>19830</v>
       </c>
       <c r="I275" t="n">
-        <v>7.52</v>
+        <v>7.5175</v>
       </c>
       <c r="J275" t="n">
-        <v>49.31</v>
+        <v>49.3125</v>
       </c>
       <c r="K275" t="n">
-        <v>49.45</v>
+        <v>49.4509</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>232345</v>
       </c>
       <c r="P275" t="n">
-        <v>95.23999999999999</v>
+        <v>95.2409</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -19512,13 +19512,13 @@
         <v>29284</v>
       </c>
       <c r="I276" t="n">
-        <v>13.45</v>
+        <v>13.4531</v>
       </c>
       <c r="J276" t="n">
-        <v>48.33</v>
+        <v>48.3333</v>
       </c>
       <c r="K276" t="n">
-        <v>48.27</v>
+        <v>48.2749</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>174712</v>
       </c>
       <c r="P276" t="n">
-        <v>92.73999999999999</v>
+        <v>92.73950000000001</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -19580,13 +19580,13 @@
         <v>26880</v>
       </c>
       <c r="I277" t="n">
-        <v>10.18</v>
+        <v>10.1815</v>
       </c>
       <c r="J277" t="n">
-        <v>49.79</v>
+        <v>49.7858</v>
       </c>
       <c r="K277" t="n">
-        <v>50.07</v>
+        <v>50.0685</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>214802</v>
       </c>
       <c r="P277" t="n">
-        <v>90.59</v>
+        <v>90.5852</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -19648,13 +19648,13 @@
         <v>37973</v>
       </c>
       <c r="I278" t="n">
-        <v>13.72</v>
+        <v>13.7249</v>
       </c>
       <c r="J278" t="n">
-        <v>48.95</v>
+        <v>48.9549</v>
       </c>
       <c r="K278" t="n">
-        <v>49.19</v>
+        <v>49.1894</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>216774</v>
       </c>
       <c r="P278" t="n">
-        <v>90.81</v>
+        <v>90.81440000000001</v>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -19716,13 +19716,13 @@
         <v>41553</v>
       </c>
       <c r="I279" t="n">
-        <v>16.13</v>
+        <v>16.1341</v>
       </c>
       <c r="J279" t="n">
-        <v>48.72</v>
+        <v>48.7235</v>
       </c>
       <c r="K279" t="n">
-        <v>48.62</v>
+        <v>48.6222</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>196484</v>
       </c>
       <c r="P279" t="n">
-        <v>90.97</v>
+        <v>90.96729999999999</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -19784,13 +19784,13 @@
         <v>36258</v>
       </c>
       <c r="I280" t="n">
-        <v>15.57</v>
+        <v>15.5745</v>
       </c>
       <c r="J280" t="n">
-        <v>48.5</v>
+        <v>48.5002</v>
       </c>
       <c r="K280" t="n">
-        <v>48.08</v>
+        <v>48.0765</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>181594</v>
       </c>
       <c r="P280" t="n">
-        <v>92.39</v>
+        <v>92.3931</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -19852,13 +19852,13 @@
         <v>45468</v>
       </c>
       <c r="I281" t="n">
-        <v>15.98</v>
+        <v>15.9818</v>
       </c>
       <c r="J281" t="n">
-        <v>49</v>
+        <v>48.9993</v>
       </c>
       <c r="K281" t="n">
-        <v>48.74</v>
+        <v>48.7353</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>215792</v>
       </c>
       <c r="P281" t="n">
-        <v>90.28</v>
+        <v>90.2782</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
@@ -19920,13 +19920,13 @@
         <v>48790</v>
       </c>
       <c r="I282" t="n">
-        <v>17.08</v>
+        <v>17.0805</v>
       </c>
       <c r="J282" t="n">
-        <v>49.72</v>
+        <v>49.7189</v>
       </c>
       <c r="K282" t="n">
-        <v>49.17</v>
+        <v>49.1733</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>210607</v>
       </c>
       <c r="P282" t="n">
-        <v>88.92</v>
+        <v>88.917</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -19988,13 +19988,13 @@
         <v>46354</v>
       </c>
       <c r="I283" t="n">
-        <v>18.04</v>
+        <v>18.0431</v>
       </c>
       <c r="J283" t="n">
-        <v>48.72</v>
+        <v>48.7215</v>
       </c>
       <c r="K283" t="n">
-        <v>47.89</v>
+        <v>47.8915</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>190239</v>
       </c>
       <c r="P283" t="n">
-        <v>90.34999999999999</v>
+        <v>90.35209999999999</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -20056,13 +20056,13 @@
         <v>33306</v>
       </c>
       <c r="I284" t="n">
-        <v>14.16</v>
+        <v>14.1605</v>
       </c>
       <c r="J284" t="n">
-        <v>49.59</v>
+        <v>49.591</v>
       </c>
       <c r="K284" t="n">
-        <v>49.18</v>
+        <v>49.1808</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>185274</v>
       </c>
       <c r="P284" t="n">
-        <v>91.77</v>
+        <v>91.76609999999999</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -20124,13 +20124,13 @@
         <v>20592</v>
       </c>
       <c r="I285" t="n">
-        <v>8.17</v>
+        <v>8.1683</v>
       </c>
       <c r="J285" t="n">
-        <v>49.06</v>
+        <v>49.0589</v>
       </c>
       <c r="K285" t="n">
-        <v>48.04</v>
+        <v>48.0383</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>220193</v>
       </c>
       <c r="P285" t="n">
-        <v>95.11</v>
+        <v>95.11450000000001</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
@@ -20192,13 +20192,13 @@
         <v>20024</v>
       </c>
       <c r="I286" t="n">
-        <v>7.36</v>
+        <v>7.3592</v>
       </c>
       <c r="J286" t="n">
-        <v>49.92</v>
+        <v>49.9193</v>
       </c>
       <c r="K286" t="n">
-        <v>49.55</v>
+        <v>49.5495</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>238504</v>
       </c>
       <c r="P286" t="n">
-        <v>94.62</v>
+        <v>94.6178</v>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
@@ -20260,13 +20260,13 @@
         <v>24761</v>
       </c>
       <c r="I287" t="n">
-        <v>8.69</v>
+        <v>8.6919</v>
       </c>
       <c r="J287" t="n">
-        <v>50.11</v>
+        <v>50.1083</v>
       </c>
       <c r="K287" t="n">
-        <v>49.62</v>
+        <v>49.6186</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>246339</v>
       </c>
       <c r="P287" t="n">
-        <v>94.7</v>
+        <v>94.705</v>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
@@ -20328,13 +20328,13 @@
         <v>18122</v>
       </c>
       <c r="I288" t="n">
-        <v>6.31</v>
+        <v>6.3098</v>
       </c>
       <c r="J288" t="n">
-        <v>49.46</v>
+        <v>49.4607</v>
       </c>
       <c r="K288" t="n">
-        <v>48.87</v>
+        <v>48.8706</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>253119</v>
       </c>
       <c r="P288" t="n">
-        <v>94.06999999999999</v>
+        <v>94.0676</v>
       </c>
       <c r="Q288" t="inlineStr">
         <is>
@@ -20396,13 +20396,13 @@
         <v>11004</v>
       </c>
       <c r="I289" t="n">
-        <v>4.48</v>
+        <v>4.4798</v>
       </c>
       <c r="J289" t="n">
-        <v>49.22</v>
+        <v>49.2216</v>
       </c>
       <c r="K289" t="n">
-        <v>48.73</v>
+        <v>48.7261</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>223002</v>
       </c>
       <c r="P289" t="n">
-        <v>95.04000000000001</v>
+        <v>95.0441</v>
       </c>
       <c r="Q289" t="inlineStr">
         <is>
@@ -20464,13 +20464,13 @@
         <v>14458</v>
       </c>
       <c r="I290" t="n">
-        <v>5.43</v>
+        <v>5.4261</v>
       </c>
       <c r="J290" t="n">
-        <v>49.79</v>
+        <v>49.7855</v>
       </c>
       <c r="K290" t="n">
-        <v>49.4</v>
+        <v>49.4042</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>241175</v>
       </c>
       <c r="P290" t="n">
-        <v>95.70999999999999</v>
+        <v>95.7055</v>
       </c>
       <c r="Q290" t="inlineStr">
         <is>
@@ -20532,13 +20532,13 @@
         <v>14207</v>
       </c>
       <c r="I291" t="n">
-        <v>5.92</v>
+        <v>5.9176</v>
       </c>
       <c r="J291" t="n">
-        <v>49.59</v>
+        <v>49.592</v>
       </c>
       <c r="K291" t="n">
-        <v>49.71</v>
+        <v>49.706</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>213473</v>
       </c>
       <c r="P291" t="n">
-        <v>94.51000000000001</v>
+        <v>94.5098</v>
       </c>
       <c r="Q291" t="inlineStr">
         <is>
@@ -20600,13 +20600,13 @@
         <v>26142</v>
       </c>
       <c r="I292" t="n">
-        <v>9.640000000000001</v>
+        <v>9.6358</v>
       </c>
       <c r="J292" t="n">
-        <v>50.6</v>
+        <v>50.5999</v>
       </c>
       <c r="K292" t="n">
-        <v>50.39</v>
+        <v>50.3865</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>233723</v>
       </c>
       <c r="P292" t="n">
-        <v>95.34</v>
+        <v>95.3353</v>
       </c>
       <c r="Q292" t="inlineStr">
         <is>
@@ -20668,13 +20668,13 @@
         <v>22011</v>
       </c>
       <c r="I293" t="n">
-        <v>8.49</v>
+        <v>8.489100000000001</v>
       </c>
       <c r="J293" t="n">
-        <v>49.53</v>
+        <v>49.526</v>
       </c>
       <c r="K293" t="n">
-        <v>49.15</v>
+        <v>49.1522</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>226555</v>
       </c>
       <c r="P293" t="n">
-        <v>95.48</v>
+        <v>95.4828</v>
       </c>
       <c r="Q293" t="inlineStr">
         <is>
@@ -20736,13 +20736,13 @@
         <v>25654</v>
       </c>
       <c r="I294" t="n">
-        <v>9.970000000000001</v>
+        <v>9.969099999999999</v>
       </c>
       <c r="J294" t="n">
-        <v>49.52</v>
+        <v>49.5187</v>
       </c>
       <c r="K294" t="n">
-        <v>49.02</v>
+        <v>49.0209</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>222519</v>
       </c>
       <c r="P294" t="n">
-        <v>96.05</v>
+        <v>96.0454</v>
       </c>
       <c r="Q294" t="inlineStr">
         <is>
@@ -20804,13 +20804,13 @@
         <v>26453</v>
       </c>
       <c r="I295" t="n">
-        <v>9.5</v>
+        <v>9.4999</v>
       </c>
       <c r="J295" t="n">
-        <v>49.45</v>
+        <v>49.4547</v>
       </c>
       <c r="K295" t="n">
-        <v>48.64</v>
+        <v>48.6385</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>242939</v>
       </c>
       <c r="P295" t="n">
-        <v>96.40000000000001</v>
+        <v>96.4028</v>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
@@ -20933,16 +20933,16 @@
         <v>1084172</v>
       </c>
       <c r="F2" t="n">
-        <v>25.87</v>
+        <v>25.8681</v>
       </c>
       <c r="G2" t="n">
-        <v>27.98</v>
+        <v>27.979</v>
       </c>
       <c r="H2" t="n">
-        <v>45.84</v>
+        <v>45.8371</v>
       </c>
       <c r="I2" t="n">
-        <v>38.67</v>
+        <v>38.6688</v>
       </c>
     </row>
     <row r="3">
@@ -20964,16 +20964,16 @@
         <v>679173</v>
       </c>
       <c r="F3" t="n">
-        <v>23.19</v>
+        <v>23.1927</v>
       </c>
       <c r="G3" t="n">
-        <v>24.54</v>
+        <v>24.5407</v>
       </c>
       <c r="H3" t="n">
-        <v>46.75</v>
+        <v>46.754</v>
       </c>
       <c r="I3" t="n">
-        <v>39.19</v>
+        <v>39.1943</v>
       </c>
     </row>
     <row r="4">
@@ -20995,16 +20995,16 @@
         <v>1965095</v>
       </c>
       <c r="F4" t="n">
-        <v>12.55</v>
+        <v>12.5487</v>
       </c>
       <c r="G4" t="n">
-        <v>14.97</v>
+        <v>14.9663</v>
       </c>
       <c r="H4" t="n">
-        <v>49.06</v>
+        <v>49.0584</v>
       </c>
       <c r="I4" t="n">
-        <v>50.32</v>
+        <v>50.316</v>
       </c>
     </row>
     <row r="5">
@@ -21026,16 +21026,16 @@
         <v>1968974</v>
       </c>
       <c r="F5" t="n">
-        <v>6.33</v>
+        <v>6.3306</v>
       </c>
       <c r="G5" t="n">
-        <v>14.19</v>
+        <v>14.1908</v>
       </c>
       <c r="H5" t="n">
-        <v>48.28</v>
+        <v>48.2794</v>
       </c>
       <c r="I5" t="n">
-        <v>55.26</v>
+        <v>55.2587</v>
       </c>
     </row>
     <row r="6">
@@ -21057,16 +21057,16 @@
         <v>7112102</v>
       </c>
       <c r="F6" t="n">
-        <v>8.890000000000001</v>
+        <v>8.886900000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>13.7</v>
+        <v>13.6976</v>
       </c>
       <c r="H6" t="n">
-        <v>49.48</v>
+        <v>49.4772</v>
       </c>
       <c r="I6" t="n">
-        <v>52.11</v>
+        <v>52.1132</v>
       </c>
     </row>
     <row r="7">
@@ -21088,16 +21088,16 @@
         <v>1110425</v>
       </c>
       <c r="F7" t="n">
-        <v>8.81</v>
+        <v>8.808400000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>13.5</v>
+        <v>13.4993</v>
       </c>
       <c r="H7" t="n">
-        <v>50.28</v>
+        <v>50.2763</v>
       </c>
       <c r="I7" t="n">
-        <v>50.24</v>
+        <v>50.245</v>
       </c>
     </row>
     <row r="8">
@@ -21119,16 +21119,16 @@
         <v>3608841</v>
       </c>
       <c r="F8" t="n">
-        <v>10.34</v>
+        <v>10.3369</v>
       </c>
       <c r="G8" t="n">
-        <v>12.39</v>
+        <v>12.3937</v>
       </c>
       <c r="H8" t="n">
-        <v>48.94</v>
+        <v>48.9431</v>
       </c>
       <c r="I8" t="n">
-        <v>50.42</v>
+        <v>50.4159</v>
       </c>
     </row>
     <row r="9">
@@ -21150,16 +21150,16 @@
         <v>1159519</v>
       </c>
       <c r="F9" t="n">
-        <v>5.34</v>
+        <v>5.3416</v>
       </c>
       <c r="G9" t="n">
-        <v>12.23</v>
+        <v>12.2331</v>
       </c>
       <c r="H9" t="n">
-        <v>48.93</v>
+        <v>48.9297</v>
       </c>
       <c r="I9" t="n">
-        <v>52.62</v>
+        <v>52.617</v>
       </c>
     </row>
     <row r="10">
@@ -21181,16 +21181,16 @@
         <v>5026213</v>
       </c>
       <c r="F10" t="n">
-        <v>3.81</v>
+        <v>3.8051</v>
       </c>
       <c r="G10" t="n">
-        <v>11.86</v>
+        <v>11.8552</v>
       </c>
       <c r="H10" t="n">
-        <v>49.23</v>
+        <v>49.2335</v>
       </c>
       <c r="I10" t="n">
-        <v>54.74</v>
+        <v>54.7374</v>
       </c>
     </row>
     <row r="11">
@@ -21212,16 +21212,16 @@
         <v>2791736</v>
       </c>
       <c r="F11" t="n">
-        <v>5.11</v>
+        <v>5.1112</v>
       </c>
       <c r="G11" t="n">
-        <v>11.63</v>
+        <v>11.6296</v>
       </c>
       <c r="H11" t="n">
-        <v>49.21</v>
+        <v>49.2108</v>
       </c>
       <c r="I11" t="n">
-        <v>55.8</v>
+        <v>55.8047</v>
       </c>
     </row>
     <row r="12">
@@ -21243,16 +21243,16 @@
         <v>7601518</v>
       </c>
       <c r="F12" t="n">
-        <v>8.789999999999999</v>
+        <v>8.789300000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>10.84</v>
+        <v>10.8391</v>
       </c>
       <c r="H12" t="n">
-        <v>49.51</v>
+        <v>49.5059</v>
       </c>
       <c r="I12" t="n">
-        <v>55.31</v>
+        <v>55.3119</v>
       </c>
     </row>
     <row r="13">
@@ -21274,16 +21274,16 @@
         <v>3954882</v>
       </c>
       <c r="F13" t="n">
-        <v>4.5</v>
+        <v>4.499</v>
       </c>
       <c r="G13" t="n">
-        <v>10.12</v>
+        <v>10.1199</v>
       </c>
       <c r="H13" t="n">
-        <v>48.64</v>
+        <v>48.6366</v>
       </c>
       <c r="I13" t="n">
-        <v>53.97</v>
+        <v>53.9667</v>
       </c>
     </row>
     <row r="14">
@@ -21305,16 +21305,16 @@
         <v>1164506</v>
       </c>
       <c r="F14" t="n">
-        <v>6.26</v>
+        <v>6.2629</v>
       </c>
       <c r="G14" t="n">
-        <v>9.35</v>
+        <v>9.3528</v>
       </c>
       <c r="H14" t="n">
-        <v>49.79</v>
+        <v>49.7875</v>
       </c>
       <c r="I14" t="n">
-        <v>54.27</v>
+        <v>54.2675</v>
       </c>
     </row>
     <row r="15">
@@ -21336,16 +21336,16 @@
         <v>1719798</v>
       </c>
       <c r="F15" t="n">
-        <v>5.86</v>
+        <v>5.8621</v>
       </c>
       <c r="G15" t="n">
-        <v>9.09</v>
+        <v>9.092700000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>49.51</v>
+        <v>49.5075</v>
       </c>
       <c r="I15" t="n">
-        <v>52.09</v>
+        <v>52.0911</v>
       </c>
     </row>
     <row r="16">
@@ -21367,16 +21367,16 @@
         <v>3771757</v>
       </c>
       <c r="F16" t="n">
-        <v>4.18</v>
+        <v>4.1825</v>
       </c>
       <c r="G16" t="n">
-        <v>8.98</v>
+        <v>8.981400000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>49.48</v>
+        <v>49.4787</v>
       </c>
       <c r="I16" t="n">
-        <v>52.06</v>
+        <v>52.0648</v>
       </c>
     </row>
     <row r="17">
@@ -21398,16 +21398,16 @@
         <v>4361392</v>
       </c>
       <c r="F17" t="n">
-        <v>6.57</v>
+        <v>6.5661</v>
       </c>
       <c r="G17" t="n">
-        <v>8.550000000000001</v>
+        <v>8.554399999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>49.75</v>
+        <v>49.7467</v>
       </c>
       <c r="I17" t="n">
-        <v>51.56</v>
+        <v>51.5633</v>
       </c>
     </row>
     <row r="18">
@@ -21429,16 +21429,16 @@
         <v>201619</v>
       </c>
       <c r="F18" t="n">
-        <v>6.85</v>
+        <v>6.8542</v>
       </c>
       <c r="G18" t="n">
-        <v>7.73</v>
+        <v>7.7292</v>
       </c>
       <c r="H18" t="n">
-        <v>50.66</v>
+        <v>50.665</v>
       </c>
       <c r="I18" t="n">
-        <v>58.82</v>
+        <v>58.8193</v>
       </c>
     </row>
     <row r="19">
@@ -21460,16 +21460,16 @@
         <v>2691386</v>
       </c>
       <c r="F19" t="n">
-        <v>5.09</v>
+        <v>5.0909</v>
       </c>
       <c r="G19" t="n">
-        <v>7.67</v>
+        <v>7.6653</v>
       </c>
       <c r="H19" t="n">
-        <v>49.67</v>
+        <v>49.6688</v>
       </c>
       <c r="I19" t="n">
-        <v>55.36</v>
+        <v>55.3583</v>
       </c>
     </row>
     <row r="20">
@@ -21491,16 +21491,16 @@
         <v>2263771</v>
       </c>
       <c r="F20" t="n">
-        <v>2.95</v>
+        <v>2.948</v>
       </c>
       <c r="G20" t="n">
-        <v>7.59</v>
+        <v>7.5874</v>
       </c>
       <c r="H20" t="n">
-        <v>48.47</v>
+        <v>48.4692</v>
       </c>
       <c r="I20" t="n">
-        <v>52.65</v>
+        <v>52.646</v>
       </c>
     </row>
     <row r="21">
@@ -21522,16 +21522,16 @@
         <v>2252807</v>
       </c>
       <c r="F21" t="n">
-        <v>6.49</v>
+        <v>6.493</v>
       </c>
       <c r="G21" t="n">
-        <v>5.88</v>
+        <v>5.8754</v>
       </c>
       <c r="H21" t="n">
-        <v>49.44</v>
+        <v>49.4388</v>
       </c>
       <c r="I21" t="n">
-        <v>62.1</v>
+        <v>62.0996</v>
       </c>
     </row>
     <row r="22">
@@ -21553,16 +21553,16 @@
         <v>3770794</v>
       </c>
       <c r="F22" t="n">
-        <v>4.28</v>
+        <v>4.2816</v>
       </c>
       <c r="G22" t="n">
-        <v>5.33</v>
+        <v>5.3301</v>
       </c>
       <c r="H22" t="n">
-        <v>49.6</v>
+        <v>49.596</v>
       </c>
       <c r="I22" t="n">
-        <v>58.51</v>
+        <v>58.5148</v>
       </c>
     </row>
     <row r="23">
@@ -21584,16 +21584,16 @@
         <v>910959</v>
       </c>
       <c r="F23" t="n">
-        <v>5.62</v>
+        <v>5.6243</v>
       </c>
       <c r="G23" t="n">
-        <v>4.69</v>
+        <v>4.6884</v>
       </c>
       <c r="H23" t="n">
-        <v>50.18</v>
+        <v>50.1827</v>
       </c>
       <c r="I23" t="n">
-        <v>60.91</v>
+        <v>60.906</v>
       </c>
     </row>
     <row r="24">
@@ -21615,16 +21615,16 @@
         <v>2919415</v>
       </c>
       <c r="F24" t="n">
-        <v>3.69</v>
+        <v>3.6906</v>
       </c>
       <c r="G24" t="n">
-        <v>3.08</v>
+        <v>3.0796</v>
       </c>
       <c r="H24" t="n">
-        <v>49.44</v>
+        <v>49.4374</v>
       </c>
       <c r="I24" t="n">
-        <v>60.71</v>
+        <v>60.7145</v>
       </c>
     </row>
     <row r="25">
@@ -21646,16 +21646,16 @@
         <v>4160154</v>
       </c>
       <c r="F25" t="n">
-        <v>2.08</v>
+        <v>2.0831</v>
       </c>
       <c r="G25" t="n">
         <v>1.64</v>
       </c>
       <c r="H25" t="n">
-        <v>48.75</v>
+        <v>48.7485</v>
       </c>
       <c r="I25" t="n">
-        <v>67.66</v>
+        <v>67.658</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/west-bengal.xlsx
+++ b/downloads/west-bengal.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>The fall in the roll is a different count from the names struck off, which were published for the state only.</t>
+          <t>The fall in the roll is a different count from the names left off the draft, which were published for the state only.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
